--- a/Product Backlog.xlsx
+++ b/Product Backlog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andij\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andij\Desktop\Arquitectura de Software Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E819FF-9040-4864-8CEF-C02B7C9466BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C03B99-4631-47BE-AC44-D4EA04AAB1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -586,9 +586,6 @@
     <t>El sistema debe garantizar una disponibilidad mínima del 99% durante el horario laboral del restaurante, evitando interrupciones que afecten la toma de órdenes, facturación o consulta de inventario.</t>
   </si>
   <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
@@ -596,6 +593,9 @@
   </si>
   <si>
     <t>Baja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioridad </t>
   </si>
 </sst>
 </file>
@@ -994,62 +994,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1076,6 +1022,60 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1312,7 +1312,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="33"/>
+      <c r="D1" s="18"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="1"/>
@@ -1341,7 +1341,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="33"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="1"/>
@@ -1370,14 +1370,14 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="19"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="43"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1401,7 +1401,7 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="33"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="1"/>
@@ -1430,7 +1430,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="33"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
@@ -1459,7 +1459,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="33"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="1"/>
@@ -1485,19 +1485,19 @@
       <c r="AA6" s="2"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="19"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="43"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -1516,19 +1516,19 @@
       <c r="AA7" s="2"/>
     </row>
     <row r="8" spans="1:27" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="19"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="43"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1547,19 +1547,19 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="19"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="43"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1581,7 +1581,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="1"/>
@@ -1607,23 +1607,23 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="39" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="24" t="s">
+      <c r="D11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="38"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -1642,15 +1642,15 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="46" t="s">
-        <v>159</v>
+      <c r="D12" s="26" t="s">
+        <v>162</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>9</v>
@@ -1691,22 +1691,22 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="41" t="s">
-        <v>160</v>
+      <c r="D13" s="21" t="s">
+        <v>159</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="32" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="12">
@@ -1742,14 +1742,14 @@
       <c r="AA13" s="5"/>
     </row>
     <row r="14" spans="1:27" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="42" t="s">
-        <v>160</v>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="22" t="s">
+        <v>159</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="28"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="13">
         <v>2</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="A15" s="14"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="41"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -1812,19 +1812,19 @@
       <c r="AA15" s="5"/>
     </row>
     <row r="16" spans="1:27" ht="265.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="41" t="s">
-        <v>161</v>
+      <c r="D16" s="21" t="s">
+        <v>160</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="20" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1863,13 +1863,13 @@
       <c r="AA16" s="5"/>
     </row>
     <row r="17" spans="1:27" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="42" t="s">
-        <v>160</v>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="22" t="s">
+        <v>159</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="20" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1911,7 +1911,7 @@
       <c r="A18" s="14"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
-      <c r="D18" s="41"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
@@ -1937,19 +1937,19 @@
       <c r="AA18" s="5"/>
     </row>
     <row r="19" spans="1:27" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="41" t="s">
-        <v>161</v>
+      <c r="D19" s="21" t="s">
+        <v>160</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="20" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1988,15 +1988,15 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="45" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="41" t="s">
-        <v>161</v>
+      <c r="D20" s="21" t="s">
+        <v>160</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="20" t="s">
         <v>54</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -2038,7 +2038,7 @@
       <c r="A21" s="14"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
-      <c r="D21" s="41"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
@@ -2070,13 +2070,13 @@
       <c r="B22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="41" t="s">
-        <v>160</v>
+      <c r="D22" s="21" t="s">
+        <v>159</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="20" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="12" t="s">
@@ -2118,7 +2118,7 @@
       <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
-      <c r="D23" s="41"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
@@ -2144,19 +2144,19 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="41" t="s">
-        <v>160</v>
+      <c r="D24" s="21" t="s">
+        <v>159</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="20" t="s">
         <v>65</v>
       </c>
       <c r="F24" s="12" t="s">
@@ -2195,13 +2195,13 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="47" t="s">
-        <v>161</v>
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="27" t="s">
+        <v>160</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="20" t="s">
         <v>70</v>
       </c>
       <c r="F25" s="12" t="s">
@@ -2240,13 +2240,13 @@
       <c r="AA25" s="2"/>
     </row>
     <row r="26" spans="1:27" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="47" t="s">
-        <v>161</v>
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="27" t="s">
+        <v>160</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F26" s="12" t="s">
@@ -2285,13 +2285,13 @@
       <c r="AA26" s="2"/>
     </row>
     <row r="27" spans="1:27" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="47" t="s">
-        <v>162</v>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="27" t="s">
+        <v>161</v>
       </c>
-      <c r="E27" s="40" t="s">
+      <c r="E27" s="20" t="s">
         <v>82</v>
       </c>
       <c r="F27" s="12" t="s">
@@ -2330,15 +2330,15 @@
       <c r="AA27" s="2"/>
     </row>
     <row r="28" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="45" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="48" t="s">
-        <v>160</v>
+      <c r="D28" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E28" s="40" t="s">
+      <c r="E28" s="20" t="s">
         <v>89</v>
       </c>
       <c r="F28" s="12" t="s">
@@ -2380,7 +2380,7 @@
       <c r="A29" s="14"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
-      <c r="D29" s="48"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2406,19 +2406,19 @@
       <c r="AA29" s="2"/>
     </row>
     <row r="30" spans="1:27" ht="193.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>160</v>
+      <c r="D30" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="20" t="s">
         <v>98</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -2457,13 +2457,13 @@
       <c r="AA30" s="2"/>
     </row>
     <row r="31" spans="1:27" ht="193.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="47" t="s">
-        <v>161</v>
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="27" t="s">
+        <v>160</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="20" t="s">
         <v>104</v>
       </c>
       <c r="F31" s="12" t="s">
@@ -2502,13 +2502,13 @@
       <c r="AA31" s="2"/>
     </row>
     <row r="32" spans="1:27" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="47" t="s">
-        <v>160</v>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="27" t="s">
+        <v>159</v>
       </c>
-      <c r="E32" s="40" t="s">
+      <c r="E32" s="20" t="s">
         <v>109</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -2547,15 +2547,15 @@
       <c r="AA32" s="2"/>
     </row>
     <row r="33" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="37" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="48" t="s">
-        <v>160</v>
+      <c r="D33" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="20" t="s">
         <v>116</v>
       </c>
       <c r="F33" s="12" t="s">
@@ -2594,15 +2594,15 @@
       <c r="AA33" s="2"/>
     </row>
     <row r="34" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="45" t="s">
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="48" t="s">
-        <v>160</v>
+      <c r="D34" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="E34" s="20" t="s">
         <v>122</v>
       </c>
       <c r="F34" s="12" t="s">
@@ -2641,15 +2641,15 @@
       <c r="AA34" s="2"/>
     </row>
     <row r="35" spans="1:27" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="45" t="s">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="D35" s="48" t="s">
-        <v>160</v>
+      <c r="D35" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="20" t="s">
         <v>129</v>
       </c>
       <c r="F35" s="12" t="s">
@@ -2691,7 +2691,7 @@
       <c r="A36" s="14"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
-      <c r="D36" s="48"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
@@ -2717,19 +2717,19 @@
       <c r="AA36" s="2"/>
     </row>
     <row r="37" spans="1:27" ht="69" x14ac:dyDescent="0.3">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="48" t="s">
-        <v>160</v>
+      <c r="D37" s="28" t="s">
+        <v>159</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="20" t="s">
         <v>135</v>
       </c>
       <c r="F37" s="12" t="s">
@@ -2768,13 +2768,13 @@
       <c r="AA37" s="2"/>
     </row>
     <row r="38" spans="1:27" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="32"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="47" t="s">
-        <v>160</v>
+      <c r="A38" s="33"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="27" t="s">
+        <v>159</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="20" t="s">
         <v>141</v>
       </c>
       <c r="F38" s="12" t="s">
@@ -2813,13 +2813,13 @@
       <c r="AA38" s="2"/>
     </row>
     <row r="39" spans="1:27" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="47" t="s">
-        <v>160</v>
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="27" t="s">
+        <v>159</v>
       </c>
-      <c r="E39" s="40" t="s">
+      <c r="E39" s="20" t="s">
         <v>147</v>
       </c>
       <c r="F39" s="12" t="s">
@@ -2858,13 +2858,13 @@
       <c r="AA39" s="2"/>
     </row>
     <row r="40" spans="1:27" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="47" t="s">
-        <v>160</v>
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="27" t="s">
+        <v>159</v>
       </c>
-      <c r="E40" s="40" t="s">
+      <c r="E40" s="20" t="s">
         <v>153</v>
       </c>
       <c r="F40" s="12" t="s">
@@ -2906,7 +2906,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="17"/>
-      <c r="D41" s="43"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="1"/>
@@ -2935,7 +2935,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="43"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="1"/>
@@ -2964,7 +2964,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="43"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="1"/>
@@ -2993,7 +2993,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="43"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="1"/>
@@ -3022,7 +3022,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="43"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="1"/>
@@ -3051,7 +3051,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="44"/>
+      <c r="D46" s="24"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="1"/>
@@ -3080,7 +3080,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="44"/>
+      <c r="D47" s="24"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="1"/>
@@ -3109,7 +3109,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="44"/>
+      <c r="D48" s="24"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="1"/>
@@ -3138,7 +3138,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="44"/>
+      <c r="D49" s="24"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="1"/>
@@ -3167,7 +3167,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="44"/>
+      <c r="D50" s="24"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="1"/>
@@ -3196,7 +3196,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="44"/>
+      <c r="D51" s="24"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="1"/>
@@ -3225,7 +3225,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="44"/>
+      <c r="D52" s="24"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="1"/>
@@ -3254,7 +3254,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="44"/>
+      <c r="D53" s="24"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="1"/>
@@ -3283,7 +3283,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="44"/>
+      <c r="D54" s="24"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="1"/>
@@ -3312,7 +3312,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="44"/>
+      <c r="D55" s="24"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="1"/>
@@ -3341,7 +3341,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="44"/>
+      <c r="D56" s="24"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="1"/>
@@ -3370,7 +3370,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="44"/>
+      <c r="D57" s="24"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="1"/>
@@ -3399,7 +3399,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="44"/>
+      <c r="D58" s="24"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="1"/>
@@ -3428,7 +3428,7 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="44"/>
+      <c r="D59" s="24"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="1"/>
@@ -3457,7 +3457,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="44"/>
+      <c r="D60" s="24"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="1"/>
@@ -3486,7 +3486,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="44"/>
+      <c r="D61" s="24"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="1"/>
@@ -3515,7 +3515,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="44"/>
+      <c r="D62" s="24"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="1"/>
@@ -3544,7 +3544,7 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="44"/>
+      <c r="D63" s="24"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="1"/>
@@ -3573,7 +3573,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="44"/>
+      <c r="D64" s="24"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="1"/>
@@ -3602,7 +3602,7 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="44"/>
+      <c r="D65" s="24"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="1"/>
@@ -3631,7 +3631,7 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="44"/>
+      <c r="D66" s="24"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="1"/>
@@ -3660,7 +3660,7 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="44"/>
+      <c r="D67" s="24"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="1"/>
@@ -3689,7 +3689,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="44"/>
+      <c r="D68" s="24"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="1"/>
@@ -3718,7 +3718,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="44"/>
+      <c r="D69" s="24"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="1"/>
@@ -3747,7 +3747,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="44"/>
+      <c r="D70" s="24"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="1"/>
@@ -3776,7 +3776,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="44"/>
+      <c r="D71" s="24"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="1"/>
@@ -3805,7 +3805,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="44"/>
+      <c r="D72" s="24"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="1"/>
@@ -3834,7 +3834,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="44"/>
+      <c r="D73" s="24"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="1"/>
@@ -3863,7 +3863,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="44"/>
+      <c r="D74" s="24"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="1"/>
@@ -3892,7 +3892,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="33"/>
+      <c r="D75" s="18"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="1"/>
@@ -3921,7 +3921,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="33"/>
+      <c r="D76" s="18"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="1"/>
@@ -3950,7 +3950,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="33"/>
+      <c r="D77" s="18"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="1"/>
@@ -3979,7 +3979,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="33"/>
+      <c r="D78" s="18"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="1"/>
@@ -4008,7 +4008,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="33"/>
+      <c r="D79" s="18"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="1"/>
@@ -4037,7 +4037,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="33"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="1"/>
@@ -4066,7 +4066,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="33"/>
+      <c r="D81" s="18"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="1"/>
@@ -4095,7 +4095,7 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="33"/>
+      <c r="D82" s="18"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="1"/>
@@ -4124,7 +4124,7 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="33"/>
+      <c r="D83" s="18"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="1"/>
@@ -4153,7 +4153,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="33"/>
+      <c r="D84" s="18"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="1"/>
@@ -4182,7 +4182,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="33"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="1"/>
@@ -4211,7 +4211,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="33"/>
+      <c r="D86" s="18"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="1"/>
@@ -4240,7 +4240,7 @@
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="33"/>
+      <c r="D87" s="18"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="1"/>
@@ -4269,7 +4269,7 @@
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="2"/>
-      <c r="D88" s="33"/>
+      <c r="D88" s="18"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="1"/>
@@ -4298,7 +4298,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="33"/>
+      <c r="D89" s="18"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="1"/>
@@ -4327,7 +4327,7 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="33"/>
+      <c r="D90" s="18"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="1"/>
@@ -4356,7 +4356,7 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="33"/>
+      <c r="D91" s="18"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="1"/>
@@ -4385,7 +4385,7 @@
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="33"/>
+      <c r="D92" s="18"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="1"/>
@@ -4414,7 +4414,7 @@
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="33"/>
+      <c r="D93" s="18"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="1"/>
@@ -4443,7 +4443,7 @@
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="33"/>
+      <c r="D94" s="18"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="1"/>
@@ -4472,7 +4472,7 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="33"/>
+      <c r="D95" s="18"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="1"/>
@@ -4501,7 +4501,7 @@
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="33"/>
+      <c r="D96" s="18"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="1"/>
@@ -4530,7 +4530,7 @@
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="33"/>
+      <c r="D97" s="18"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="1"/>
@@ -4559,7 +4559,7 @@
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="33"/>
+      <c r="D98" s="18"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="1"/>
@@ -4588,7 +4588,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="33"/>
+      <c r="D99" s="18"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="1"/>
@@ -4617,7 +4617,7 @@
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="33"/>
+      <c r="D100" s="18"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="1"/>
@@ -4646,7 +4646,7 @@
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="33"/>
+      <c r="D101" s="18"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="1"/>
@@ -4675,7 +4675,7 @@
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="33"/>
+      <c r="D102" s="18"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="1"/>
@@ -4704,7 +4704,7 @@
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="33"/>
+      <c r="D103" s="18"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="1"/>
@@ -4733,7 +4733,7 @@
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="33"/>
+      <c r="D104" s="18"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="1"/>
@@ -4762,7 +4762,7 @@
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="33"/>
+      <c r="D105" s="18"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="1"/>
@@ -4791,7 +4791,7 @@
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="33"/>
+      <c r="D106" s="18"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="1"/>
@@ -4820,7 +4820,7 @@
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="33"/>
+      <c r="D107" s="18"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="1"/>
@@ -4849,7 +4849,7 @@
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="33"/>
+      <c r="D108" s="18"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="1"/>
@@ -4878,7 +4878,7 @@
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="33"/>
+      <c r="D109" s="18"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="1"/>
@@ -4907,7 +4907,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="33"/>
+      <c r="D110" s="18"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="1"/>
@@ -4936,7 +4936,7 @@
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="33"/>
+      <c r="D111" s="18"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="1"/>
@@ -4965,7 +4965,7 @@
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="33"/>
+      <c r="D112" s="18"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="1"/>
@@ -4994,7 +4994,7 @@
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="33"/>
+      <c r="D113" s="18"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="1"/>
@@ -5023,7 +5023,7 @@
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="33"/>
+      <c r="D114" s="18"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="1"/>
@@ -5052,7 +5052,7 @@
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="33"/>
+      <c r="D115" s="18"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="1"/>
@@ -5081,7 +5081,7 @@
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="33"/>
+      <c r="D116" s="18"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="1"/>
@@ -5110,7 +5110,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="33"/>
+      <c r="D117" s="18"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="1"/>
@@ -5139,7 +5139,7 @@
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="33"/>
+      <c r="D118" s="18"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="1"/>
@@ -5168,7 +5168,7 @@
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="33"/>
+      <c r="D119" s="18"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="1"/>
@@ -5197,7 +5197,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="33"/>
+      <c r="D120" s="18"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="1"/>
@@ -5226,7 +5226,7 @@
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="33"/>
+      <c r="D121" s="18"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="1"/>
@@ -5255,7 +5255,7 @@
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="33"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="1"/>
@@ -5284,7 +5284,7 @@
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="33"/>
+      <c r="D123" s="18"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="1"/>
@@ -5313,7 +5313,7 @@
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="33"/>
+      <c r="D124" s="18"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="1"/>
@@ -5342,7 +5342,7 @@
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="33"/>
+      <c r="D125" s="18"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="1"/>
@@ -5371,7 +5371,7 @@
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="33"/>
+      <c r="D126" s="18"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="1"/>
@@ -5400,7 +5400,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="33"/>
+      <c r="D127" s="18"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="1"/>
@@ -5429,7 +5429,7 @@
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="33"/>
+      <c r="D128" s="18"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="1"/>
@@ -5458,7 +5458,7 @@
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="33"/>
+      <c r="D129" s="18"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="1"/>
@@ -5487,7 +5487,7 @@
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="33"/>
+      <c r="D130" s="18"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="1"/>
@@ -5516,7 +5516,7 @@
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="33"/>
+      <c r="D131" s="18"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="1"/>
@@ -5545,7 +5545,7 @@
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="33"/>
+      <c r="D132" s="18"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="1"/>
@@ -5574,7 +5574,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="33"/>
+      <c r="D133" s="18"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="1"/>
@@ -5603,7 +5603,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="33"/>
+      <c r="D134" s="18"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="1"/>
@@ -5632,7 +5632,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="33"/>
+      <c r="D135" s="18"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="1"/>
@@ -5661,7 +5661,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="33"/>
+      <c r="D136" s="18"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="1"/>
@@ -5690,7 +5690,7 @@
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="33"/>
+      <c r="D137" s="18"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="1"/>
@@ -5719,7 +5719,7 @@
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="33"/>
+      <c r="D138" s="18"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="1"/>
@@ -5748,7 +5748,7 @@
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="33"/>
+      <c r="D139" s="18"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="1"/>
@@ -5777,7 +5777,7 @@
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="33"/>
+      <c r="D140" s="18"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="1"/>
@@ -5806,7 +5806,7 @@
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="33"/>
+      <c r="D141" s="18"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="1"/>
@@ -5835,7 +5835,7 @@
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="33"/>
+      <c r="D142" s="18"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="1"/>
@@ -5864,7 +5864,7 @@
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="33"/>
+      <c r="D143" s="18"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="1"/>
@@ -5893,7 +5893,7 @@
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="33"/>
+      <c r="D144" s="18"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="1"/>
@@ -5922,7 +5922,7 @@
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="33"/>
+      <c r="D145" s="18"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="1"/>
@@ -5951,7 +5951,7 @@
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="33"/>
+      <c r="D146" s="18"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="1"/>
@@ -5980,7 +5980,7 @@
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="33"/>
+      <c r="D147" s="18"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="1"/>
@@ -6009,7 +6009,7 @@
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="33"/>
+      <c r="D148" s="18"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="1"/>
@@ -6038,7 +6038,7 @@
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="33"/>
+      <c r="D149" s="18"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="1"/>
@@ -6067,7 +6067,7 @@
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="33"/>
+      <c r="D150" s="18"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="1"/>
@@ -6096,7 +6096,7 @@
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="33"/>
+      <c r="D151" s="18"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="1"/>
@@ -6125,7 +6125,7 @@
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="33"/>
+      <c r="D152" s="18"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="1"/>
@@ -6154,7 +6154,7 @@
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="33"/>
+      <c r="D153" s="18"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="1"/>
@@ -6183,7 +6183,7 @@
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="33"/>
+      <c r="D154" s="18"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="1"/>
@@ -6212,7 +6212,7 @@
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="33"/>
+      <c r="D155" s="18"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="1"/>
@@ -6241,7 +6241,7 @@
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="33"/>
+      <c r="D156" s="18"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="1"/>
@@ -6270,7 +6270,7 @@
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="33"/>
+      <c r="D157" s="18"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="1"/>
@@ -6299,7 +6299,7 @@
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="33"/>
+      <c r="D158" s="18"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="1"/>
@@ -6328,7 +6328,7 @@
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="33"/>
+      <c r="D159" s="18"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="1"/>
@@ -6357,7 +6357,7 @@
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="33"/>
+      <c r="D160" s="18"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="1"/>
@@ -6386,7 +6386,7 @@
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="33"/>
+      <c r="D161" s="18"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="1"/>
@@ -6415,7 +6415,7 @@
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="33"/>
+      <c r="D162" s="18"/>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="1"/>
@@ -6444,7 +6444,7 @@
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="33"/>
+      <c r="D163" s="18"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="1"/>
@@ -6473,7 +6473,7 @@
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="33"/>
+      <c r="D164" s="18"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="1"/>
@@ -6502,7 +6502,7 @@
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="33"/>
+      <c r="D165" s="18"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="1"/>
@@ -6531,7 +6531,7 @@
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="33"/>
+      <c r="D166" s="18"/>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="1"/>
@@ -6560,7 +6560,7 @@
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="33"/>
+      <c r="D167" s="18"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="1"/>
@@ -6589,7 +6589,7 @@
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="33"/>
+      <c r="D168" s="18"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="1"/>
@@ -6618,7 +6618,7 @@
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="33"/>
+      <c r="D169" s="18"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="1"/>
@@ -6647,7 +6647,7 @@
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="33"/>
+      <c r="D170" s="18"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="1"/>
@@ -6676,7 +6676,7 @@
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="33"/>
+      <c r="D171" s="18"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="1"/>
@@ -6705,7 +6705,7 @@
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="33"/>
+      <c r="D172" s="18"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="1"/>
@@ -6734,7 +6734,7 @@
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="33"/>
+      <c r="D173" s="18"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="1"/>
@@ -6763,7 +6763,7 @@
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="33"/>
+      <c r="D174" s="18"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="1"/>
@@ -6792,7 +6792,7 @@
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="33"/>
+      <c r="D175" s="18"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="1"/>
@@ -6821,7 +6821,7 @@
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="33"/>
+      <c r="D176" s="18"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="1"/>
@@ -6850,7 +6850,7 @@
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="33"/>
+      <c r="D177" s="18"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="1"/>
@@ -6879,7 +6879,7 @@
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="33"/>
+      <c r="D178" s="18"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="1"/>
@@ -6908,7 +6908,7 @@
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="33"/>
+      <c r="D179" s="18"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="1"/>
@@ -6937,7 +6937,7 @@
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="33"/>
+      <c r="D180" s="18"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="1"/>
@@ -6966,7 +6966,7 @@
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="33"/>
+      <c r="D181" s="18"/>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="1"/>
@@ -6995,7 +6995,7 @@
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="33"/>
+      <c r="D182" s="18"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="1"/>
@@ -7024,7 +7024,7 @@
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="33"/>
+      <c r="D183" s="18"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="1"/>
@@ -7053,7 +7053,7 @@
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="33"/>
+      <c r="D184" s="18"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="1"/>
@@ -7082,7 +7082,7 @@
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="33"/>
+      <c r="D185" s="18"/>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="1"/>
@@ -7111,7 +7111,7 @@
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="33"/>
+      <c r="D186" s="18"/>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="1"/>
@@ -7140,7 +7140,7 @@
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="33"/>
+      <c r="D187" s="18"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="1"/>
@@ -7169,7 +7169,7 @@
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="33"/>
+      <c r="D188" s="18"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="1"/>
@@ -7198,7 +7198,7 @@
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="33"/>
+      <c r="D189" s="18"/>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="1"/>
@@ -7227,7 +7227,7 @@
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="33"/>
+      <c r="D190" s="18"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="1"/>
@@ -7256,7 +7256,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="33"/>
+      <c r="D191" s="18"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="1"/>
@@ -7285,7 +7285,7 @@
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="33"/>
+      <c r="D192" s="18"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="1"/>
@@ -7314,7 +7314,7 @@
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="33"/>
+      <c r="D193" s="18"/>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="1"/>
@@ -7343,7 +7343,7 @@
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="33"/>
+      <c r="D194" s="18"/>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="1"/>
@@ -7372,7 +7372,7 @@
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="33"/>
+      <c r="D195" s="18"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="1"/>
@@ -7401,7 +7401,7 @@
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="33"/>
+      <c r="D196" s="18"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="1"/>
@@ -7430,7 +7430,7 @@
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="33"/>
+      <c r="D197" s="18"/>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="1"/>
@@ -7459,7 +7459,7 @@
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="33"/>
+      <c r="D198" s="18"/>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="1"/>
@@ -7488,7 +7488,7 @@
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="33"/>
+      <c r="D199" s="18"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="1"/>
@@ -7517,7 +7517,7 @@
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="33"/>
+      <c r="D200" s="18"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="1"/>
@@ -7546,7 +7546,7 @@
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="33"/>
+      <c r="D201" s="18"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="1"/>
@@ -7575,7 +7575,7 @@
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="33"/>
+      <c r="D202" s="18"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="1"/>
@@ -7604,7 +7604,7 @@
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="33"/>
+      <c r="D203" s="18"/>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="1"/>
@@ -7633,7 +7633,7 @@
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="33"/>
+      <c r="D204" s="18"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="1"/>
@@ -7662,7 +7662,7 @@
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="33"/>
+      <c r="D205" s="18"/>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="1"/>
@@ -7691,7 +7691,7 @@
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="33"/>
+      <c r="D206" s="18"/>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="1"/>
@@ -7720,7 +7720,7 @@
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="33"/>
+      <c r="D207" s="18"/>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="1"/>
@@ -7749,7 +7749,7 @@
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="33"/>
+      <c r="D208" s="18"/>
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="1"/>
@@ -7778,7 +7778,7 @@
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="33"/>
+      <c r="D209" s="18"/>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="1"/>
@@ -7807,7 +7807,7 @@
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="33"/>
+      <c r="D210" s="18"/>
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="1"/>
@@ -7836,7 +7836,7 @@
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="33"/>
+      <c r="D211" s="18"/>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="1"/>
@@ -7865,7 +7865,7 @@
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="33"/>
+      <c r="D212" s="18"/>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="1"/>
@@ -7894,7 +7894,7 @@
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="33"/>
+      <c r="D213" s="18"/>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="1"/>
@@ -7923,7 +7923,7 @@
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="33"/>
+      <c r="D214" s="18"/>
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="1"/>
@@ -7952,7 +7952,7 @@
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="33"/>
+      <c r="D215" s="18"/>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="1"/>
@@ -7981,7 +7981,7 @@
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="33"/>
+      <c r="D216" s="18"/>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="1"/>
@@ -8010,7 +8010,7 @@
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="33"/>
+      <c r="D217" s="18"/>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="1"/>
@@ -8039,7 +8039,7 @@
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="33"/>
+      <c r="D218" s="18"/>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="1"/>
@@ -8068,7 +8068,7 @@
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="33"/>
+      <c r="D219" s="18"/>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="1"/>
@@ -8097,7 +8097,7 @@
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="33"/>
+      <c r="D220" s="18"/>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="1"/>
@@ -8126,7 +8126,7 @@
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="33"/>
+      <c r="D221" s="18"/>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="G221" s="1"/>
@@ -8155,7 +8155,7 @@
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="33"/>
+      <c r="D222" s="18"/>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="1"/>
@@ -8184,7 +8184,7 @@
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="33"/>
+      <c r="D223" s="18"/>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="1"/>
@@ -8213,7 +8213,7 @@
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="33"/>
+      <c r="D224" s="18"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="1"/>
@@ -8242,7 +8242,7 @@
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="33"/>
+      <c r="D225" s="18"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="1"/>
@@ -8271,7 +8271,7 @@
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="33"/>
+      <c r="D226" s="18"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="1"/>
@@ -8300,7 +8300,7 @@
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="33"/>
+      <c r="D227" s="18"/>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="1"/>
@@ -8329,7 +8329,7 @@
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="33"/>
+      <c r="D228" s="18"/>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="1"/>
@@ -8358,7 +8358,7 @@
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="33"/>
+      <c r="D229" s="18"/>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="1"/>
@@ -8387,7 +8387,7 @@
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="33"/>
+      <c r="D230" s="18"/>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="G230" s="1"/>
@@ -8416,7 +8416,7 @@
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="2"/>
-      <c r="D231" s="33"/>
+      <c r="D231" s="18"/>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="1"/>
@@ -8445,7 +8445,7 @@
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="2"/>
-      <c r="D232" s="33"/>
+      <c r="D232" s="18"/>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="G232" s="1"/>
@@ -8474,7 +8474,7 @@
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="2"/>
-      <c r="D233" s="33"/>
+      <c r="D233" s="18"/>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="G233" s="1"/>
@@ -8503,7 +8503,7 @@
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="2"/>
-      <c r="D234" s="33"/>
+      <c r="D234" s="18"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="1"/>
@@ -8532,7 +8532,7 @@
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="2"/>
-      <c r="D235" s="33"/>
+      <c r="D235" s="18"/>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="G235" s="1"/>
@@ -8561,7 +8561,7 @@
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="2"/>
-      <c r="D236" s="33"/>
+      <c r="D236" s="18"/>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="1"/>
@@ -8590,7 +8590,7 @@
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="2"/>
-      <c r="D237" s="33"/>
+      <c r="D237" s="18"/>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="G237" s="1"/>
@@ -8619,7 +8619,7 @@
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="2"/>
-      <c r="D238" s="33"/>
+      <c r="D238" s="18"/>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="G238" s="1"/>
@@ -8648,7 +8648,7 @@
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="2"/>
-      <c r="D239" s="33"/>
+      <c r="D239" s="18"/>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="1"/>
@@ -8677,7 +8677,7 @@
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="2"/>
-      <c r="D240" s="33"/>
+      <c r="D240" s="18"/>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="1"/>
@@ -8706,7 +8706,7 @@
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="2"/>
-      <c r="D241" s="33"/>
+      <c r="D241" s="18"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="1"/>
@@ -8735,7 +8735,7 @@
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="2"/>
-      <c r="D242" s="33"/>
+      <c r="D242" s="18"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="1"/>
@@ -8764,7 +8764,7 @@
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="2"/>
-      <c r="D243" s="33"/>
+      <c r="D243" s="18"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="1"/>
@@ -8793,7 +8793,7 @@
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="2"/>
-      <c r="D244" s="33"/>
+      <c r="D244" s="18"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="1"/>
@@ -8822,7 +8822,7 @@
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="2"/>
-      <c r="D245" s="33"/>
+      <c r="D245" s="18"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="1"/>
@@ -8851,7 +8851,7 @@
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="2"/>
-      <c r="D246" s="33"/>
+      <c r="D246" s="18"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="1"/>
@@ -8880,7 +8880,7 @@
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="2"/>
-      <c r="D247" s="33"/>
+      <c r="D247" s="18"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="1"/>
@@ -8909,7 +8909,7 @@
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="2"/>
-      <c r="D248" s="33"/>
+      <c r="D248" s="18"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="G248" s="1"/>
@@ -8938,7 +8938,7 @@
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="2"/>
-      <c r="D249" s="33"/>
+      <c r="D249" s="18"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="G249" s="1"/>
@@ -8967,7 +8967,7 @@
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="2"/>
-      <c r="D250" s="33"/>
+      <c r="D250" s="18"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="1"/>
@@ -8996,7 +8996,7 @@
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="2"/>
-      <c r="D251" s="33"/>
+      <c r="D251" s="18"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="1"/>
@@ -9025,7 +9025,7 @@
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="2"/>
-      <c r="D252" s="33"/>
+      <c r="D252" s="18"/>
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
       <c r="G252" s="1"/>
@@ -9054,7 +9054,7 @@
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="2"/>
-      <c r="D253" s="33"/>
+      <c r="D253" s="18"/>
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="G253" s="1"/>
@@ -9083,7 +9083,7 @@
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="2"/>
-      <c r="D254" s="33"/>
+      <c r="D254" s="18"/>
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="G254" s="1"/>
@@ -9112,7 +9112,7 @@
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="2"/>
-      <c r="D255" s="33"/>
+      <c r="D255" s="18"/>
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
       <c r="G255" s="1"/>
@@ -9141,7 +9141,7 @@
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="2"/>
-      <c r="D256" s="33"/>
+      <c r="D256" s="18"/>
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
       <c r="G256" s="1"/>
@@ -9170,7 +9170,7 @@
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="2"/>
-      <c r="D257" s="33"/>
+      <c r="D257" s="18"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
       <c r="G257" s="1"/>
@@ -9199,7 +9199,7 @@
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="2"/>
-      <c r="D258" s="33"/>
+      <c r="D258" s="18"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
       <c r="G258" s="1"/>
@@ -9228,7 +9228,7 @@
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="2"/>
-      <c r="D259" s="33"/>
+      <c r="D259" s="18"/>
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
       <c r="G259" s="1"/>
@@ -9257,7 +9257,7 @@
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="2"/>
-      <c r="D260" s="33"/>
+      <c r="D260" s="18"/>
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
       <c r="G260" s="1"/>
@@ -9286,7 +9286,7 @@
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="2"/>
-      <c r="D261" s="33"/>
+      <c r="D261" s="18"/>
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
       <c r="G261" s="1"/>
@@ -9315,7 +9315,7 @@
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="2"/>
-      <c r="D262" s="33"/>
+      <c r="D262" s="18"/>
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
       <c r="G262" s="1"/>
@@ -9344,7 +9344,7 @@
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="2"/>
-      <c r="D263" s="33"/>
+      <c r="D263" s="18"/>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
       <c r="G263" s="1"/>
@@ -9373,7 +9373,7 @@
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="2"/>
-      <c r="D264" s="33"/>
+      <c r="D264" s="18"/>
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
       <c r="G264" s="1"/>
@@ -9402,7 +9402,7 @@
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="2"/>
-      <c r="D265" s="33"/>
+      <c r="D265" s="18"/>
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
       <c r="G265" s="1"/>
@@ -9431,7 +9431,7 @@
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="2"/>
-      <c r="D266" s="33"/>
+      <c r="D266" s="18"/>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
       <c r="G266" s="1"/>
@@ -9460,7 +9460,7 @@
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="2"/>
-      <c r="D267" s="33"/>
+      <c r="D267" s="18"/>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
       <c r="G267" s="1"/>
@@ -9489,7 +9489,7 @@
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="2"/>
-      <c r="D268" s="33"/>
+      <c r="D268" s="18"/>
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
       <c r="G268" s="1"/>
@@ -9518,7 +9518,7 @@
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="2"/>
-      <c r="D269" s="33"/>
+      <c r="D269" s="18"/>
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
       <c r="G269" s="1"/>
@@ -9547,7 +9547,7 @@
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="33"/>
+      <c r="D270" s="18"/>
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
       <c r="G270" s="1"/>
@@ -9576,7 +9576,7 @@
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="2"/>
-      <c r="D271" s="33"/>
+      <c r="D271" s="18"/>
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
       <c r="G271" s="1"/>
@@ -9605,7 +9605,7 @@
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="33"/>
+      <c r="D272" s="18"/>
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
       <c r="G272" s="1"/>
@@ -9634,7 +9634,7 @@
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="2"/>
-      <c r="D273" s="33"/>
+      <c r="D273" s="18"/>
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
       <c r="G273" s="1"/>
@@ -9663,7 +9663,7 @@
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="2"/>
-      <c r="D274" s="33"/>
+      <c r="D274" s="18"/>
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="1"/>
@@ -9692,7 +9692,7 @@
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="2"/>
-      <c r="D275" s="33"/>
+      <c r="D275" s="18"/>
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
       <c r="G275" s="1"/>
@@ -9721,7 +9721,7 @@
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="2"/>
-      <c r="D276" s="33"/>
+      <c r="D276" s="18"/>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
       <c r="G276" s="1"/>
@@ -9750,7 +9750,7 @@
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="2"/>
-      <c r="D277" s="33"/>
+      <c r="D277" s="18"/>
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
       <c r="G277" s="1"/>
@@ -9779,7 +9779,7 @@
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="2"/>
-      <c r="D278" s="33"/>
+      <c r="D278" s="18"/>
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
       <c r="G278" s="1"/>
@@ -9808,7 +9808,7 @@
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="2"/>
-      <c r="D279" s="33"/>
+      <c r="D279" s="18"/>
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="G279" s="1"/>
@@ -9837,7 +9837,7 @@
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="2"/>
-      <c r="D280" s="33"/>
+      <c r="D280" s="18"/>
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
       <c r="G280" s="1"/>
@@ -9866,7 +9866,7 @@
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="2"/>
-      <c r="D281" s="33"/>
+      <c r="D281" s="18"/>
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
       <c r="G281" s="1"/>
@@ -9895,7 +9895,7 @@
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="2"/>
-      <c r="D282" s="33"/>
+      <c r="D282" s="18"/>
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
       <c r="G282" s="1"/>
@@ -9924,7 +9924,7 @@
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="2"/>
-      <c r="D283" s="33"/>
+      <c r="D283" s="18"/>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
       <c r="G283" s="1"/>
@@ -9953,7 +9953,7 @@
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="2"/>
-      <c r="D284" s="33"/>
+      <c r="D284" s="18"/>
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
       <c r="G284" s="1"/>
@@ -9982,7 +9982,7 @@
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="2"/>
-      <c r="D285" s="33"/>
+      <c r="D285" s="18"/>
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="G285" s="1"/>
@@ -10011,7 +10011,7 @@
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="2"/>
-      <c r="D286" s="33"/>
+      <c r="D286" s="18"/>
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
       <c r="G286" s="1"/>
@@ -10040,7 +10040,7 @@
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="2"/>
-      <c r="D287" s="33"/>
+      <c r="D287" s="18"/>
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
       <c r="G287" s="1"/>
@@ -10069,7 +10069,7 @@
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="2"/>
-      <c r="D288" s="33"/>
+      <c r="D288" s="18"/>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
       <c r="G288" s="1"/>
@@ -10098,7 +10098,7 @@
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="2"/>
-      <c r="D289" s="33"/>
+      <c r="D289" s="18"/>
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
       <c r="G289" s="1"/>
@@ -10127,7 +10127,7 @@
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="2"/>
-      <c r="D290" s="33"/>
+      <c r="D290" s="18"/>
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="G290" s="1"/>
@@ -10156,7 +10156,7 @@
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="2"/>
-      <c r="D291" s="33"/>
+      <c r="D291" s="18"/>
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="G291" s="1"/>
@@ -10185,7 +10185,7 @@
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="2"/>
-      <c r="D292" s="33"/>
+      <c r="D292" s="18"/>
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
       <c r="G292" s="1"/>
@@ -10214,7 +10214,7 @@
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="2"/>
-      <c r="D293" s="33"/>
+      <c r="D293" s="18"/>
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
       <c r="G293" s="1"/>
@@ -10243,7 +10243,7 @@
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="2"/>
-      <c r="D294" s="33"/>
+      <c r="D294" s="18"/>
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
       <c r="G294" s="1"/>
@@ -10272,7 +10272,7 @@
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="2"/>
-      <c r="D295" s="33"/>
+      <c r="D295" s="18"/>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
       <c r="G295" s="1"/>
@@ -10301,7 +10301,7 @@
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="2"/>
-      <c r="D296" s="33"/>
+      <c r="D296" s="18"/>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
       <c r="G296" s="1"/>
@@ -10330,7 +10330,7 @@
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="2"/>
-      <c r="D297" s="33"/>
+      <c r="D297" s="18"/>
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
       <c r="G297" s="1"/>
@@ -10359,7 +10359,7 @@
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="2"/>
-      <c r="D298" s="33"/>
+      <c r="D298" s="18"/>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
       <c r="G298" s="1"/>
@@ -10388,7 +10388,7 @@
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="2"/>
-      <c r="D299" s="33"/>
+      <c r="D299" s="18"/>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
       <c r="G299" s="1"/>
@@ -10417,7 +10417,7 @@
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="2"/>
-      <c r="D300" s="33"/>
+      <c r="D300" s="18"/>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="1"/>
@@ -10446,7 +10446,7 @@
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="2"/>
-      <c r="D301" s="33"/>
+      <c r="D301" s="18"/>
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
       <c r="G301" s="1"/>
@@ -10475,7 +10475,7 @@
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="2"/>
-      <c r="D302" s="33"/>
+      <c r="D302" s="18"/>
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="G302" s="1"/>
@@ -10504,7 +10504,7 @@
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="2"/>
-      <c r="D303" s="33"/>
+      <c r="D303" s="18"/>
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="1"/>
@@ -10533,7 +10533,7 @@
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="2"/>
-      <c r="D304" s="33"/>
+      <c r="D304" s="18"/>
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
       <c r="G304" s="1"/>
@@ -10562,7 +10562,7 @@
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="2"/>
-      <c r="D305" s="33"/>
+      <c r="D305" s="18"/>
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
       <c r="G305" s="1"/>
@@ -10591,7 +10591,7 @@
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="2"/>
-      <c r="D306" s="33"/>
+      <c r="D306" s="18"/>
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
       <c r="G306" s="1"/>
@@ -10620,7 +10620,7 @@
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="2"/>
-      <c r="D307" s="33"/>
+      <c r="D307" s="18"/>
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
       <c r="G307" s="1"/>
@@ -10649,7 +10649,7 @@
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="2"/>
-      <c r="D308" s="33"/>
+      <c r="D308" s="18"/>
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
       <c r="G308" s="1"/>
@@ -10678,7 +10678,7 @@
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="2"/>
-      <c r="D309" s="33"/>
+      <c r="D309" s="18"/>
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
       <c r="G309" s="1"/>
@@ -10707,7 +10707,7 @@
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="2"/>
-      <c r="D310" s="33"/>
+      <c r="D310" s="18"/>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
       <c r="G310" s="1"/>
@@ -10736,7 +10736,7 @@
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="2"/>
-      <c r="D311" s="33"/>
+      <c r="D311" s="18"/>
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
       <c r="G311" s="1"/>
@@ -10765,7 +10765,7 @@
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="2"/>
-      <c r="D312" s="33"/>
+      <c r="D312" s="18"/>
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
       <c r="G312" s="1"/>
@@ -10794,7 +10794,7 @@
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="2"/>
-      <c r="D313" s="33"/>
+      <c r="D313" s="18"/>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
       <c r="G313" s="1"/>
@@ -10823,7 +10823,7 @@
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="2"/>
-      <c r="D314" s="33"/>
+      <c r="D314" s="18"/>
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
       <c r="G314" s="1"/>
@@ -10852,7 +10852,7 @@
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="2"/>
-      <c r="D315" s="33"/>
+      <c r="D315" s="18"/>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="G315" s="1"/>
@@ -10881,7 +10881,7 @@
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="2"/>
-      <c r="D316" s="33"/>
+      <c r="D316" s="18"/>
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="1"/>
@@ -10910,7 +10910,7 @@
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="2"/>
-      <c r="D317" s="33"/>
+      <c r="D317" s="18"/>
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
       <c r="G317" s="1"/>
@@ -10939,7 +10939,7 @@
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="2"/>
-      <c r="D318" s="33"/>
+      <c r="D318" s="18"/>
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
       <c r="G318" s="1"/>
@@ -10968,7 +10968,7 @@
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="2"/>
-      <c r="D319" s="33"/>
+      <c r="D319" s="18"/>
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
       <c r="G319" s="1"/>
@@ -10997,7 +10997,7 @@
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="2"/>
-      <c r="D320" s="33"/>
+      <c r="D320" s="18"/>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="G320" s="1"/>
@@ -11026,7 +11026,7 @@
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="2"/>
-      <c r="D321" s="33"/>
+      <c r="D321" s="18"/>
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="G321" s="1"/>
@@ -11055,7 +11055,7 @@
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="2"/>
-      <c r="D322" s="33"/>
+      <c r="D322" s="18"/>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
       <c r="G322" s="1"/>
@@ -11084,7 +11084,7 @@
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="2"/>
-      <c r="D323" s="33"/>
+      <c r="D323" s="18"/>
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
       <c r="G323" s="1"/>
@@ -11113,7 +11113,7 @@
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="2"/>
-      <c r="D324" s="33"/>
+      <c r="D324" s="18"/>
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
       <c r="G324" s="1"/>
@@ -11142,7 +11142,7 @@
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="2"/>
-      <c r="D325" s="33"/>
+      <c r="D325" s="18"/>
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
       <c r="G325" s="1"/>
@@ -11171,7 +11171,7 @@
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="2"/>
-      <c r="D326" s="33"/>
+      <c r="D326" s="18"/>
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="G326" s="1"/>
@@ -11200,7 +11200,7 @@
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="2"/>
-      <c r="D327" s="33"/>
+      <c r="D327" s="18"/>
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
       <c r="G327" s="1"/>
@@ -11229,7 +11229,7 @@
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="2"/>
-      <c r="D328" s="33"/>
+      <c r="D328" s="18"/>
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="G328" s="1"/>
@@ -11258,7 +11258,7 @@
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="2"/>
-      <c r="D329" s="33"/>
+      <c r="D329" s="18"/>
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
       <c r="G329" s="1"/>
@@ -11287,7 +11287,7 @@
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="2"/>
-      <c r="D330" s="33"/>
+      <c r="D330" s="18"/>
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
       <c r="G330" s="1"/>
@@ -11316,7 +11316,7 @@
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="2"/>
-      <c r="D331" s="33"/>
+      <c r="D331" s="18"/>
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
       <c r="G331" s="1"/>
@@ -11345,7 +11345,7 @@
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="2"/>
-      <c r="D332" s="33"/>
+      <c r="D332" s="18"/>
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="1"/>
@@ -11374,7 +11374,7 @@
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="2"/>
-      <c r="D333" s="33"/>
+      <c r="D333" s="18"/>
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
       <c r="G333" s="1"/>
@@ -11403,7 +11403,7 @@
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="2"/>
-      <c r="D334" s="33"/>
+      <c r="D334" s="18"/>
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
       <c r="G334" s="1"/>
@@ -11432,7 +11432,7 @@
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="2"/>
-      <c r="D335" s="33"/>
+      <c r="D335" s="18"/>
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
       <c r="G335" s="1"/>
@@ -11461,7 +11461,7 @@
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="2"/>
-      <c r="D336" s="33"/>
+      <c r="D336" s="18"/>
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
       <c r="G336" s="1"/>
@@ -11490,7 +11490,7 @@
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="2"/>
-      <c r="D337" s="33"/>
+      <c r="D337" s="18"/>
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
       <c r="G337" s="1"/>
@@ -11519,7 +11519,7 @@
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="2"/>
-      <c r="D338" s="33"/>
+      <c r="D338" s="18"/>
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
       <c r="G338" s="1"/>
@@ -11548,7 +11548,7 @@
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="2"/>
-      <c r="D339" s="33"/>
+      <c r="D339" s="18"/>
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
       <c r="G339" s="1"/>
@@ -11577,7 +11577,7 @@
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="2"/>
-      <c r="D340" s="33"/>
+      <c r="D340" s="18"/>
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
       <c r="G340" s="1"/>
@@ -11606,7 +11606,7 @@
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="2"/>
-      <c r="D341" s="33"/>
+      <c r="D341" s="18"/>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="G341" s="1"/>
@@ -11635,7 +11635,7 @@
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="2"/>
-      <c r="D342" s="33"/>
+      <c r="D342" s="18"/>
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
       <c r="G342" s="1"/>
@@ -11664,7 +11664,7 @@
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="2"/>
-      <c r="D343" s="33"/>
+      <c r="D343" s="18"/>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
       <c r="G343" s="1"/>
@@ -11693,7 +11693,7 @@
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="2"/>
-      <c r="D344" s="33"/>
+      <c r="D344" s="18"/>
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
       <c r="G344" s="1"/>
@@ -11722,7 +11722,7 @@
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="2"/>
-      <c r="D345" s="33"/>
+      <c r="D345" s="18"/>
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
       <c r="G345" s="1"/>
@@ -11751,7 +11751,7 @@
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="2"/>
-      <c r="D346" s="33"/>
+      <c r="D346" s="18"/>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
       <c r="G346" s="1"/>
@@ -11780,7 +11780,7 @@
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="2"/>
-      <c r="D347" s="33"/>
+      <c r="D347" s="18"/>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
       <c r="G347" s="1"/>
@@ -11809,7 +11809,7 @@
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="2"/>
-      <c r="D348" s="33"/>
+      <c r="D348" s="18"/>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
       <c r="G348" s="1"/>
@@ -11838,7 +11838,7 @@
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="2"/>
-      <c r="D349" s="33"/>
+      <c r="D349" s="18"/>
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
       <c r="G349" s="1"/>
@@ -11867,7 +11867,7 @@
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="2"/>
-      <c r="D350" s="33"/>
+      <c r="D350" s="18"/>
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
       <c r="G350" s="1"/>
@@ -11896,7 +11896,7 @@
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="2"/>
-      <c r="D351" s="33"/>
+      <c r="D351" s="18"/>
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
       <c r="G351" s="1"/>
@@ -11925,7 +11925,7 @@
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="2"/>
-      <c r="D352" s="33"/>
+      <c r="D352" s="18"/>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
       <c r="G352" s="1"/>
@@ -11954,7 +11954,7 @@
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="2"/>
-      <c r="D353" s="33"/>
+      <c r="D353" s="18"/>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
       <c r="G353" s="1"/>
@@ -11983,7 +11983,7 @@
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="2"/>
-      <c r="D354" s="33"/>
+      <c r="D354" s="18"/>
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
       <c r="G354" s="1"/>
@@ -12012,7 +12012,7 @@
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="2"/>
-      <c r="D355" s="33"/>
+      <c r="D355" s="18"/>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
       <c r="G355" s="1"/>
@@ -12041,7 +12041,7 @@
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="2"/>
-      <c r="D356" s="33"/>
+      <c r="D356" s="18"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
       <c r="G356" s="1"/>
@@ -12070,7 +12070,7 @@
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="2"/>
-      <c r="D357" s="33"/>
+      <c r="D357" s="18"/>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
       <c r="G357" s="1"/>
@@ -12099,7 +12099,7 @@
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="2"/>
-      <c r="D358" s="33"/>
+      <c r="D358" s="18"/>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
       <c r="G358" s="1"/>
@@ -12128,7 +12128,7 @@
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="2"/>
-      <c r="D359" s="33"/>
+      <c r="D359" s="18"/>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
       <c r="G359" s="1"/>
@@ -12157,7 +12157,7 @@
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="2"/>
-      <c r="D360" s="33"/>
+      <c r="D360" s="18"/>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
       <c r="G360" s="1"/>
@@ -12186,7 +12186,7 @@
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="2"/>
-      <c r="D361" s="33"/>
+      <c r="D361" s="18"/>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="1"/>
@@ -12215,7 +12215,7 @@
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="2"/>
-      <c r="D362" s="33"/>
+      <c r="D362" s="18"/>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
       <c r="G362" s="1"/>
@@ -12244,7 +12244,7 @@
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="2"/>
-      <c r="D363" s="33"/>
+      <c r="D363" s="18"/>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
       <c r="G363" s="1"/>
@@ -12273,7 +12273,7 @@
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="2"/>
-      <c r="D364" s="33"/>
+      <c r="D364" s="18"/>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
       <c r="G364" s="1"/>
@@ -12302,7 +12302,7 @@
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="2"/>
-      <c r="D365" s="33"/>
+      <c r="D365" s="18"/>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
       <c r="G365" s="1"/>
@@ -12331,7 +12331,7 @@
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="2"/>
-      <c r="D366" s="33"/>
+      <c r="D366" s="18"/>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
       <c r="G366" s="1"/>
@@ -12360,7 +12360,7 @@
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="2"/>
-      <c r="D367" s="33"/>
+      <c r="D367" s="18"/>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
       <c r="G367" s="1"/>
@@ -12389,7 +12389,7 @@
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="2"/>
-      <c r="D368" s="33"/>
+      <c r="D368" s="18"/>
       <c r="E368" s="3"/>
       <c r="F368" s="3"/>
       <c r="G368" s="1"/>
@@ -12418,7 +12418,7 @@
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="2"/>
-      <c r="D369" s="33"/>
+      <c r="D369" s="18"/>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
       <c r="G369" s="1"/>
@@ -12447,7 +12447,7 @@
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="2"/>
-      <c r="D370" s="33"/>
+      <c r="D370" s="18"/>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
       <c r="G370" s="1"/>
@@ -12476,7 +12476,7 @@
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="2"/>
-      <c r="D371" s="33"/>
+      <c r="D371" s="18"/>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
       <c r="G371" s="1"/>
@@ -12505,7 +12505,7 @@
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="2"/>
-      <c r="D372" s="33"/>
+      <c r="D372" s="18"/>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
       <c r="G372" s="1"/>
@@ -12534,7 +12534,7 @@
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="2"/>
-      <c r="D373" s="33"/>
+      <c r="D373" s="18"/>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
       <c r="G373" s="1"/>
@@ -12563,7 +12563,7 @@
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="2"/>
-      <c r="D374" s="33"/>
+      <c r="D374" s="18"/>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
       <c r="G374" s="1"/>
@@ -12592,7 +12592,7 @@
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="2"/>
-      <c r="D375" s="33"/>
+      <c r="D375" s="18"/>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
       <c r="G375" s="1"/>
@@ -12621,7 +12621,7 @@
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="2"/>
-      <c r="D376" s="33"/>
+      <c r="D376" s="18"/>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
       <c r="G376" s="1"/>
@@ -12650,7 +12650,7 @@
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="2"/>
-      <c r="D377" s="33"/>
+      <c r="D377" s="18"/>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
       <c r="G377" s="1"/>
@@ -12679,7 +12679,7 @@
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="2"/>
-      <c r="D378" s="33"/>
+      <c r="D378" s="18"/>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
       <c r="G378" s="1"/>
@@ -12708,7 +12708,7 @@
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="2"/>
-      <c r="D379" s="33"/>
+      <c r="D379" s="18"/>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
       <c r="G379" s="1"/>
@@ -12737,7 +12737,7 @@
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="2"/>
-      <c r="D380" s="33"/>
+      <c r="D380" s="18"/>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
       <c r="G380" s="1"/>
@@ -12766,7 +12766,7 @@
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="2"/>
-      <c r="D381" s="33"/>
+      <c r="D381" s="18"/>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
       <c r="G381" s="1"/>
@@ -12795,7 +12795,7 @@
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="2"/>
-      <c r="D382" s="33"/>
+      <c r="D382" s="18"/>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
       <c r="G382" s="1"/>
@@ -12824,7 +12824,7 @@
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="2"/>
-      <c r="D383" s="33"/>
+      <c r="D383" s="18"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
       <c r="G383" s="1"/>
@@ -12853,7 +12853,7 @@
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="2"/>
-      <c r="D384" s="33"/>
+      <c r="D384" s="18"/>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
       <c r="G384" s="1"/>
@@ -12882,7 +12882,7 @@
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="2"/>
-      <c r="D385" s="33"/>
+      <c r="D385" s="18"/>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
       <c r="G385" s="1"/>
@@ -12911,7 +12911,7 @@
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="2"/>
-      <c r="D386" s="33"/>
+      <c r="D386" s="18"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
       <c r="G386" s="1"/>
@@ -12940,7 +12940,7 @@
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="2"/>
-      <c r="D387" s="33"/>
+      <c r="D387" s="18"/>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
       <c r="G387" s="1"/>
@@ -12969,7 +12969,7 @@
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="2"/>
-      <c r="D388" s="33"/>
+      <c r="D388" s="18"/>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
       <c r="G388" s="1"/>
@@ -12998,7 +12998,7 @@
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="2"/>
-      <c r="D389" s="33"/>
+      <c r="D389" s="18"/>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
       <c r="G389" s="1"/>
@@ -13027,7 +13027,7 @@
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="2"/>
-      <c r="D390" s="33"/>
+      <c r="D390" s="18"/>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="1"/>
@@ -13056,7 +13056,7 @@
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="2"/>
-      <c r="D391" s="33"/>
+      <c r="D391" s="18"/>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
       <c r="G391" s="1"/>
@@ -13085,7 +13085,7 @@
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="2"/>
-      <c r="D392" s="33"/>
+      <c r="D392" s="18"/>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
       <c r="G392" s="1"/>
@@ -13114,7 +13114,7 @@
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="2"/>
-      <c r="D393" s="33"/>
+      <c r="D393" s="18"/>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
       <c r="G393" s="1"/>
@@ -13143,7 +13143,7 @@
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="2"/>
-      <c r="D394" s="33"/>
+      <c r="D394" s="18"/>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
       <c r="G394" s="1"/>
@@ -13172,7 +13172,7 @@
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="2"/>
-      <c r="D395" s="33"/>
+      <c r="D395" s="18"/>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
       <c r="G395" s="1"/>
@@ -13201,7 +13201,7 @@
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="2"/>
-      <c r="D396" s="33"/>
+      <c r="D396" s="18"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
       <c r="G396" s="1"/>
@@ -13230,7 +13230,7 @@
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="2"/>
-      <c r="D397" s="33"/>
+      <c r="D397" s="18"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
       <c r="G397" s="1"/>
@@ -13259,7 +13259,7 @@
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="2"/>
-      <c r="D398" s="33"/>
+      <c r="D398" s="18"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
       <c r="G398" s="1"/>
@@ -13288,7 +13288,7 @@
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="2"/>
-      <c r="D399" s="33"/>
+      <c r="D399" s="18"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
       <c r="G399" s="1"/>
@@ -13317,7 +13317,7 @@
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="2"/>
-      <c r="D400" s="33"/>
+      <c r="D400" s="18"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
       <c r="G400" s="1"/>
@@ -13346,7 +13346,7 @@
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="2"/>
-      <c r="D401" s="33"/>
+      <c r="D401" s="18"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
       <c r="G401" s="1"/>
@@ -13375,7 +13375,7 @@
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="2"/>
-      <c r="D402" s="33"/>
+      <c r="D402" s="18"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
       <c r="G402" s="1"/>
@@ -13404,7 +13404,7 @@
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="2"/>
-      <c r="D403" s="33"/>
+      <c r="D403" s="18"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
       <c r="G403" s="1"/>
@@ -13433,7 +13433,7 @@
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="2"/>
-      <c r="D404" s="33"/>
+      <c r="D404" s="18"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
       <c r="G404" s="1"/>
@@ -13462,7 +13462,7 @@
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="2"/>
-      <c r="D405" s="33"/>
+      <c r="D405" s="18"/>
       <c r="E405" s="3"/>
       <c r="F405" s="3"/>
       <c r="G405" s="1"/>
@@ -13491,7 +13491,7 @@
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="2"/>
-      <c r="D406" s="33"/>
+      <c r="D406" s="18"/>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
       <c r="G406" s="1"/>
@@ -13520,7 +13520,7 @@
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="2"/>
-      <c r="D407" s="33"/>
+      <c r="D407" s="18"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
       <c r="G407" s="1"/>
@@ -13549,7 +13549,7 @@
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="2"/>
-      <c r="D408" s="33"/>
+      <c r="D408" s="18"/>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
       <c r="G408" s="1"/>
@@ -13578,7 +13578,7 @@
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="2"/>
-      <c r="D409" s="33"/>
+      <c r="D409" s="18"/>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
       <c r="G409" s="1"/>
@@ -13607,7 +13607,7 @@
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="2"/>
-      <c r="D410" s="33"/>
+      <c r="D410" s="18"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="1"/>
@@ -13636,7 +13636,7 @@
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="2"/>
-      <c r="D411" s="33"/>
+      <c r="D411" s="18"/>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
       <c r="G411" s="1"/>
@@ -13665,7 +13665,7 @@
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="2"/>
-      <c r="D412" s="33"/>
+      <c r="D412" s="18"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
       <c r="G412" s="1"/>
@@ -13694,7 +13694,7 @@
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="2"/>
-      <c r="D413" s="33"/>
+      <c r="D413" s="18"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
       <c r="G413" s="1"/>
@@ -13723,7 +13723,7 @@
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="2"/>
-      <c r="D414" s="33"/>
+      <c r="D414" s="18"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
       <c r="G414" s="1"/>
@@ -13752,7 +13752,7 @@
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="2"/>
-      <c r="D415" s="33"/>
+      <c r="D415" s="18"/>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
       <c r="G415" s="1"/>
@@ -13781,7 +13781,7 @@
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="2"/>
-      <c r="D416" s="33"/>
+      <c r="D416" s="18"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
       <c r="G416" s="1"/>
@@ -13810,7 +13810,7 @@
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="2"/>
-      <c r="D417" s="33"/>
+      <c r="D417" s="18"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
       <c r="G417" s="1"/>
@@ -13839,7 +13839,7 @@
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="2"/>
-      <c r="D418" s="33"/>
+      <c r="D418" s="18"/>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
       <c r="G418" s="1"/>
@@ -13868,7 +13868,7 @@
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="2"/>
-      <c r="D419" s="33"/>
+      <c r="D419" s="18"/>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="1"/>
@@ -13897,7 +13897,7 @@
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="2"/>
-      <c r="D420" s="33"/>
+      <c r="D420" s="18"/>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
       <c r="G420" s="1"/>
@@ -13926,7 +13926,7 @@
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="2"/>
-      <c r="D421" s="33"/>
+      <c r="D421" s="18"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
       <c r="G421" s="1"/>
@@ -13955,7 +13955,7 @@
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="2"/>
-      <c r="D422" s="33"/>
+      <c r="D422" s="18"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
       <c r="G422" s="1"/>
@@ -13984,7 +13984,7 @@
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="2"/>
-      <c r="D423" s="33"/>
+      <c r="D423" s="18"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
       <c r="G423" s="1"/>
@@ -14013,7 +14013,7 @@
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="2"/>
-      <c r="D424" s="33"/>
+      <c r="D424" s="18"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
       <c r="G424" s="1"/>
@@ -14042,7 +14042,7 @@
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="2"/>
-      <c r="D425" s="33"/>
+      <c r="D425" s="18"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
       <c r="G425" s="1"/>
@@ -14071,7 +14071,7 @@
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="2"/>
-      <c r="D426" s="33"/>
+      <c r="D426" s="18"/>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
       <c r="G426" s="1"/>
@@ -14100,7 +14100,7 @@
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="2"/>
-      <c r="D427" s="33"/>
+      <c r="D427" s="18"/>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
       <c r="G427" s="1"/>
@@ -14129,7 +14129,7 @@
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="2"/>
-      <c r="D428" s="33"/>
+      <c r="D428" s="18"/>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
       <c r="G428" s="1"/>
@@ -14158,7 +14158,7 @@
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="2"/>
-      <c r="D429" s="33"/>
+      <c r="D429" s="18"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
       <c r="G429" s="1"/>
@@ -14187,7 +14187,7 @@
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="2"/>
-      <c r="D430" s="33"/>
+      <c r="D430" s="18"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
       <c r="G430" s="1"/>
@@ -14216,7 +14216,7 @@
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="2"/>
-      <c r="D431" s="33"/>
+      <c r="D431" s="18"/>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
       <c r="G431" s="1"/>
@@ -14245,7 +14245,7 @@
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="2"/>
-      <c r="D432" s="33"/>
+      <c r="D432" s="18"/>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
       <c r="G432" s="1"/>
@@ -14274,7 +14274,7 @@
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="2"/>
-      <c r="D433" s="33"/>
+      <c r="D433" s="18"/>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
       <c r="G433" s="1"/>
@@ -14303,7 +14303,7 @@
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="2"/>
-      <c r="D434" s="33"/>
+      <c r="D434" s="18"/>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
       <c r="G434" s="1"/>
@@ -14332,7 +14332,7 @@
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="2"/>
-      <c r="D435" s="33"/>
+      <c r="D435" s="18"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
       <c r="G435" s="1"/>
@@ -14361,7 +14361,7 @@
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="2"/>
-      <c r="D436" s="33"/>
+      <c r="D436" s="18"/>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
       <c r="G436" s="1"/>
@@ -14390,7 +14390,7 @@
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="2"/>
-      <c r="D437" s="33"/>
+      <c r="D437" s="18"/>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
       <c r="G437" s="1"/>
@@ -14419,7 +14419,7 @@
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="2"/>
-      <c r="D438" s="33"/>
+      <c r="D438" s="18"/>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
       <c r="G438" s="1"/>
@@ -14448,7 +14448,7 @@
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="2"/>
-      <c r="D439" s="33"/>
+      <c r="D439" s="18"/>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
       <c r="G439" s="1"/>
@@ -14477,7 +14477,7 @@
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="2"/>
-      <c r="D440" s="33"/>
+      <c r="D440" s="18"/>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
       <c r="G440" s="1"/>
@@ -14506,7 +14506,7 @@
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="2"/>
-      <c r="D441" s="33"/>
+      <c r="D441" s="18"/>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
       <c r="G441" s="1"/>
@@ -14535,7 +14535,7 @@
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="2"/>
-      <c r="D442" s="33"/>
+      <c r="D442" s="18"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
       <c r="G442" s="1"/>
@@ -14564,7 +14564,7 @@
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="2"/>
-      <c r="D443" s="33"/>
+      <c r="D443" s="18"/>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
       <c r="G443" s="1"/>
@@ -14593,7 +14593,7 @@
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="2"/>
-      <c r="D444" s="33"/>
+      <c r="D444" s="18"/>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
       <c r="G444" s="1"/>
@@ -14622,7 +14622,7 @@
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="2"/>
-      <c r="D445" s="33"/>
+      <c r="D445" s="18"/>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
       <c r="G445" s="1"/>
@@ -14651,7 +14651,7 @@
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="2"/>
-      <c r="D446" s="33"/>
+      <c r="D446" s="18"/>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
       <c r="G446" s="1"/>
@@ -14680,7 +14680,7 @@
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="2"/>
-      <c r="D447" s="33"/>
+      <c r="D447" s="18"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
       <c r="G447" s="1"/>
@@ -14709,7 +14709,7 @@
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="2"/>
-      <c r="D448" s="33"/>
+      <c r="D448" s="18"/>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="1"/>
@@ -14738,7 +14738,7 @@
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="2"/>
-      <c r="D449" s="33"/>
+      <c r="D449" s="18"/>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
       <c r="G449" s="1"/>
@@ -14767,7 +14767,7 @@
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="2"/>
-      <c r="D450" s="33"/>
+      <c r="D450" s="18"/>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
       <c r="G450" s="1"/>
@@ -14796,7 +14796,7 @@
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="2"/>
-      <c r="D451" s="33"/>
+      <c r="D451" s="18"/>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
       <c r="G451" s="1"/>
@@ -14825,7 +14825,7 @@
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="2"/>
-      <c r="D452" s="33"/>
+      <c r="D452" s="18"/>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
       <c r="G452" s="1"/>
@@ -14854,7 +14854,7 @@
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="2"/>
-      <c r="D453" s="33"/>
+      <c r="D453" s="18"/>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
       <c r="G453" s="1"/>
@@ -14883,7 +14883,7 @@
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="2"/>
-      <c r="D454" s="33"/>
+      <c r="D454" s="18"/>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
       <c r="G454" s="1"/>
@@ -14912,7 +14912,7 @@
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="2"/>
-      <c r="D455" s="33"/>
+      <c r="D455" s="18"/>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
       <c r="G455" s="1"/>
@@ -14941,7 +14941,7 @@
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="2"/>
-      <c r="D456" s="33"/>
+      <c r="D456" s="18"/>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
       <c r="G456" s="1"/>
@@ -14970,7 +14970,7 @@
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="2"/>
-      <c r="D457" s="33"/>
+      <c r="D457" s="18"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
       <c r="G457" s="1"/>
@@ -14999,7 +14999,7 @@
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="2"/>
-      <c r="D458" s="33"/>
+      <c r="D458" s="18"/>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
       <c r="G458" s="1"/>
@@ -15028,7 +15028,7 @@
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="2"/>
-      <c r="D459" s="33"/>
+      <c r="D459" s="18"/>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
       <c r="G459" s="1"/>
@@ -15057,7 +15057,7 @@
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="2"/>
-      <c r="D460" s="33"/>
+      <c r="D460" s="18"/>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
       <c r="G460" s="1"/>
@@ -15086,7 +15086,7 @@
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="2"/>
-      <c r="D461" s="33"/>
+      <c r="D461" s="18"/>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
       <c r="G461" s="1"/>
@@ -15115,7 +15115,7 @@
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="2"/>
-      <c r="D462" s="33"/>
+      <c r="D462" s="18"/>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
       <c r="G462" s="1"/>
@@ -15144,7 +15144,7 @@
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="2"/>
-      <c r="D463" s="33"/>
+      <c r="D463" s="18"/>
       <c r="E463" s="3"/>
       <c r="F463" s="3"/>
       <c r="G463" s="1"/>
@@ -15173,7 +15173,7 @@
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="2"/>
-      <c r="D464" s="33"/>
+      <c r="D464" s="18"/>
       <c r="E464" s="3"/>
       <c r="F464" s="3"/>
       <c r="G464" s="1"/>
@@ -15202,7 +15202,7 @@
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="2"/>
-      <c r="D465" s="33"/>
+      <c r="D465" s="18"/>
       <c r="E465" s="3"/>
       <c r="F465" s="3"/>
       <c r="G465" s="1"/>
@@ -15231,7 +15231,7 @@
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="2"/>
-      <c r="D466" s="33"/>
+      <c r="D466" s="18"/>
       <c r="E466" s="3"/>
       <c r="F466" s="3"/>
       <c r="G466" s="1"/>
@@ -15260,7 +15260,7 @@
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="2"/>
-      <c r="D467" s="33"/>
+      <c r="D467" s="18"/>
       <c r="E467" s="3"/>
       <c r="F467" s="3"/>
       <c r="G467" s="1"/>
@@ -15289,7 +15289,7 @@
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="2"/>
-      <c r="D468" s="33"/>
+      <c r="D468" s="18"/>
       <c r="E468" s="3"/>
       <c r="F468" s="3"/>
       <c r="G468" s="1"/>
@@ -15318,7 +15318,7 @@
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="2"/>
-      <c r="D469" s="33"/>
+      <c r="D469" s="18"/>
       <c r="E469" s="3"/>
       <c r="F469" s="3"/>
       <c r="G469" s="1"/>
@@ -15347,7 +15347,7 @@
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="2"/>
-      <c r="D470" s="33"/>
+      <c r="D470" s="18"/>
       <c r="E470" s="3"/>
       <c r="F470" s="3"/>
       <c r="G470" s="1"/>
@@ -15376,7 +15376,7 @@
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="2"/>
-      <c r="D471" s="33"/>
+      <c r="D471" s="18"/>
       <c r="E471" s="3"/>
       <c r="F471" s="3"/>
       <c r="G471" s="1"/>
@@ -15405,7 +15405,7 @@
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="2"/>
-      <c r="D472" s="33"/>
+      <c r="D472" s="18"/>
       <c r="E472" s="3"/>
       <c r="F472" s="3"/>
       <c r="G472" s="1"/>
@@ -15434,7 +15434,7 @@
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="2"/>
-      <c r="D473" s="33"/>
+      <c r="D473" s="18"/>
       <c r="E473" s="3"/>
       <c r="F473" s="3"/>
       <c r="G473" s="1"/>
@@ -15463,7 +15463,7 @@
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="2"/>
-      <c r="D474" s="33"/>
+      <c r="D474" s="18"/>
       <c r="E474" s="3"/>
       <c r="F474" s="3"/>
       <c r="G474" s="1"/>
@@ -15492,7 +15492,7 @@
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="2"/>
-      <c r="D475" s="33"/>
+      <c r="D475" s="18"/>
       <c r="E475" s="3"/>
       <c r="F475" s="3"/>
       <c r="G475" s="1"/>
@@ -15521,7 +15521,7 @@
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="2"/>
-      <c r="D476" s="33"/>
+      <c r="D476" s="18"/>
       <c r="E476" s="3"/>
       <c r="F476" s="3"/>
       <c r="G476" s="1"/>
@@ -15550,7 +15550,7 @@
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="2"/>
-      <c r="D477" s="33"/>
+      <c r="D477" s="18"/>
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="1"/>
@@ -15579,7 +15579,7 @@
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="2"/>
-      <c r="D478" s="33"/>
+      <c r="D478" s="18"/>
       <c r="E478" s="3"/>
       <c r="F478" s="3"/>
       <c r="G478" s="1"/>
@@ -15608,7 +15608,7 @@
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="2"/>
-      <c r="D479" s="33"/>
+      <c r="D479" s="18"/>
       <c r="E479" s="3"/>
       <c r="F479" s="3"/>
       <c r="G479" s="1"/>
@@ -15637,7 +15637,7 @@
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="2"/>
-      <c r="D480" s="33"/>
+      <c r="D480" s="18"/>
       <c r="E480" s="3"/>
       <c r="F480" s="3"/>
       <c r="G480" s="1"/>
@@ -15666,7 +15666,7 @@
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="2"/>
-      <c r="D481" s="33"/>
+      <c r="D481" s="18"/>
       <c r="E481" s="3"/>
       <c r="F481" s="3"/>
       <c r="G481" s="1"/>
@@ -15695,7 +15695,7 @@
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="2"/>
-      <c r="D482" s="33"/>
+      <c r="D482" s="18"/>
       <c r="E482" s="3"/>
       <c r="F482" s="3"/>
       <c r="G482" s="1"/>
@@ -15724,7 +15724,7 @@
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="2"/>
-      <c r="D483" s="33"/>
+      <c r="D483" s="18"/>
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
       <c r="G483" s="1"/>
@@ -15753,7 +15753,7 @@
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="2"/>
-      <c r="D484" s="33"/>
+      <c r="D484" s="18"/>
       <c r="E484" s="3"/>
       <c r="F484" s="3"/>
       <c r="G484" s="1"/>
@@ -15782,7 +15782,7 @@
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="2"/>
-      <c r="D485" s="33"/>
+      <c r="D485" s="18"/>
       <c r="E485" s="3"/>
       <c r="F485" s="3"/>
       <c r="G485" s="1"/>
@@ -15811,7 +15811,7 @@
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="2"/>
-      <c r="D486" s="33"/>
+      <c r="D486" s="18"/>
       <c r="E486" s="3"/>
       <c r="F486" s="3"/>
       <c r="G486" s="1"/>
@@ -15840,7 +15840,7 @@
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="2"/>
-      <c r="D487" s="33"/>
+      <c r="D487" s="18"/>
       <c r="E487" s="3"/>
       <c r="F487" s="3"/>
       <c r="G487" s="1"/>
@@ -15869,7 +15869,7 @@
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="2"/>
-      <c r="D488" s="33"/>
+      <c r="D488" s="18"/>
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
       <c r="G488" s="1"/>
@@ -15898,7 +15898,7 @@
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="2"/>
-      <c r="D489" s="33"/>
+      <c r="D489" s="18"/>
       <c r="E489" s="3"/>
       <c r="F489" s="3"/>
       <c r="G489" s="1"/>
@@ -15927,7 +15927,7 @@
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="2"/>
-      <c r="D490" s="33"/>
+      <c r="D490" s="18"/>
       <c r="E490" s="3"/>
       <c r="F490" s="3"/>
       <c r="G490" s="1"/>
@@ -15956,7 +15956,7 @@
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="2"/>
-      <c r="D491" s="33"/>
+      <c r="D491" s="18"/>
       <c r="E491" s="3"/>
       <c r="F491" s="3"/>
       <c r="G491" s="1"/>
@@ -15985,7 +15985,7 @@
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="2"/>
-      <c r="D492" s="33"/>
+      <c r="D492" s="18"/>
       <c r="E492" s="3"/>
       <c r="F492" s="3"/>
       <c r="G492" s="1"/>
@@ -16014,7 +16014,7 @@
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="2"/>
-      <c r="D493" s="33"/>
+      <c r="D493" s="18"/>
       <c r="E493" s="3"/>
       <c r="F493" s="3"/>
       <c r="G493" s="1"/>
@@ -16043,7 +16043,7 @@
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="2"/>
-      <c r="D494" s="33"/>
+      <c r="D494" s="18"/>
       <c r="E494" s="3"/>
       <c r="F494" s="3"/>
       <c r="G494" s="1"/>
@@ -16072,7 +16072,7 @@
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="2"/>
-      <c r="D495" s="33"/>
+      <c r="D495" s="18"/>
       <c r="E495" s="3"/>
       <c r="F495" s="3"/>
       <c r="G495" s="1"/>
@@ -16101,7 +16101,7 @@
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="2"/>
-      <c r="D496" s="33"/>
+      <c r="D496" s="18"/>
       <c r="E496" s="3"/>
       <c r="F496" s="3"/>
       <c r="G496" s="1"/>
@@ -16130,7 +16130,7 @@
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="2"/>
-      <c r="D497" s="33"/>
+      <c r="D497" s="18"/>
       <c r="E497" s="3"/>
       <c r="F497" s="3"/>
       <c r="G497" s="1"/>
@@ -16159,7 +16159,7 @@
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="2"/>
-      <c r="D498" s="33"/>
+      <c r="D498" s="18"/>
       <c r="E498" s="3"/>
       <c r="F498" s="3"/>
       <c r="G498" s="1"/>
@@ -16188,7 +16188,7 @@
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="2"/>
-      <c r="D499" s="33"/>
+      <c r="D499" s="18"/>
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
       <c r="G499" s="1"/>
@@ -16217,7 +16217,7 @@
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="2"/>
-      <c r="D500" s="33"/>
+      <c r="D500" s="18"/>
       <c r="E500" s="3"/>
       <c r="F500" s="3"/>
       <c r="G500" s="1"/>
@@ -16246,7 +16246,7 @@
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="2"/>
-      <c r="D501" s="33"/>
+      <c r="D501" s="18"/>
       <c r="E501" s="3"/>
       <c r="F501" s="3"/>
       <c r="G501" s="1"/>
@@ -16275,7 +16275,7 @@
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="2"/>
-      <c r="D502" s="33"/>
+      <c r="D502" s="18"/>
       <c r="E502" s="3"/>
       <c r="F502" s="3"/>
       <c r="G502" s="1"/>
@@ -16304,7 +16304,7 @@
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="2"/>
-      <c r="D503" s="33"/>
+      <c r="D503" s="18"/>
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
       <c r="G503" s="1"/>
@@ -16333,7 +16333,7 @@
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="2"/>
-      <c r="D504" s="33"/>
+      <c r="D504" s="18"/>
       <c r="E504" s="3"/>
       <c r="F504" s="3"/>
       <c r="G504" s="1"/>
@@ -16362,7 +16362,7 @@
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="2"/>
-      <c r="D505" s="33"/>
+      <c r="D505" s="18"/>
       <c r="E505" s="3"/>
       <c r="F505" s="3"/>
       <c r="G505" s="1"/>
@@ -16391,7 +16391,7 @@
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="2"/>
-      <c r="D506" s="33"/>
+      <c r="D506" s="18"/>
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="1"/>
@@ -16420,7 +16420,7 @@
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="2"/>
-      <c r="D507" s="33"/>
+      <c r="D507" s="18"/>
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
       <c r="G507" s="1"/>
@@ -16449,7 +16449,7 @@
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="2"/>
-      <c r="D508" s="33"/>
+      <c r="D508" s="18"/>
       <c r="E508" s="3"/>
       <c r="F508" s="3"/>
       <c r="G508" s="1"/>
@@ -16478,7 +16478,7 @@
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="2"/>
-      <c r="D509" s="33"/>
+      <c r="D509" s="18"/>
       <c r="E509" s="3"/>
       <c r="F509" s="3"/>
       <c r="G509" s="1"/>
@@ -16507,7 +16507,7 @@
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="2"/>
-      <c r="D510" s="33"/>
+      <c r="D510" s="18"/>
       <c r="E510" s="3"/>
       <c r="F510" s="3"/>
       <c r="G510" s="1"/>
@@ -16536,7 +16536,7 @@
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="2"/>
-      <c r="D511" s="33"/>
+      <c r="D511" s="18"/>
       <c r="E511" s="3"/>
       <c r="F511" s="3"/>
       <c r="G511" s="1"/>
@@ -16565,7 +16565,7 @@
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="2"/>
-      <c r="D512" s="33"/>
+      <c r="D512" s="18"/>
       <c r="E512" s="3"/>
       <c r="F512" s="3"/>
       <c r="G512" s="1"/>
@@ -16594,7 +16594,7 @@
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="2"/>
-      <c r="D513" s="33"/>
+      <c r="D513" s="18"/>
       <c r="E513" s="3"/>
       <c r="F513" s="3"/>
       <c r="G513" s="1"/>
@@ -16623,7 +16623,7 @@
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="2"/>
-      <c r="D514" s="33"/>
+      <c r="D514" s="18"/>
       <c r="E514" s="3"/>
       <c r="F514" s="3"/>
       <c r="G514" s="1"/>
@@ -16652,7 +16652,7 @@
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="2"/>
-      <c r="D515" s="33"/>
+      <c r="D515" s="18"/>
       <c r="E515" s="3"/>
       <c r="F515" s="3"/>
       <c r="G515" s="1"/>
@@ -16681,7 +16681,7 @@
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="2"/>
-      <c r="D516" s="33"/>
+      <c r="D516" s="18"/>
       <c r="E516" s="3"/>
       <c r="F516" s="3"/>
       <c r="G516" s="1"/>
@@ -16710,7 +16710,7 @@
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="2"/>
-      <c r="D517" s="33"/>
+      <c r="D517" s="18"/>
       <c r="E517" s="3"/>
       <c r="F517" s="3"/>
       <c r="G517" s="1"/>
@@ -16739,7 +16739,7 @@
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="2"/>
-      <c r="D518" s="33"/>
+      <c r="D518" s="18"/>
       <c r="E518" s="3"/>
       <c r="F518" s="3"/>
       <c r="G518" s="1"/>
@@ -16768,7 +16768,7 @@
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="2"/>
-      <c r="D519" s="33"/>
+      <c r="D519" s="18"/>
       <c r="E519" s="3"/>
       <c r="F519" s="3"/>
       <c r="G519" s="1"/>
@@ -16797,7 +16797,7 @@
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="2"/>
-      <c r="D520" s="33"/>
+      <c r="D520" s="18"/>
       <c r="E520" s="3"/>
       <c r="F520" s="3"/>
       <c r="G520" s="1"/>
@@ -16826,7 +16826,7 @@
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="2"/>
-      <c r="D521" s="33"/>
+      <c r="D521" s="18"/>
       <c r="E521" s="3"/>
       <c r="F521" s="3"/>
       <c r="G521" s="1"/>
@@ -16855,7 +16855,7 @@
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="2"/>
-      <c r="D522" s="33"/>
+      <c r="D522" s="18"/>
       <c r="E522" s="3"/>
       <c r="F522" s="3"/>
       <c r="G522" s="1"/>
@@ -16884,7 +16884,7 @@
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="2"/>
-      <c r="D523" s="33"/>
+      <c r="D523" s="18"/>
       <c r="E523" s="3"/>
       <c r="F523" s="3"/>
       <c r="G523" s="1"/>
@@ -16913,7 +16913,7 @@
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="2"/>
-      <c r="D524" s="33"/>
+      <c r="D524" s="18"/>
       <c r="E524" s="3"/>
       <c r="F524" s="3"/>
       <c r="G524" s="1"/>
@@ -16942,7 +16942,7 @@
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="2"/>
-      <c r="D525" s="33"/>
+      <c r="D525" s="18"/>
       <c r="E525" s="3"/>
       <c r="F525" s="3"/>
       <c r="G525" s="1"/>
@@ -16971,7 +16971,7 @@
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="2"/>
-      <c r="D526" s="33"/>
+      <c r="D526" s="18"/>
       <c r="E526" s="3"/>
       <c r="F526" s="3"/>
       <c r="G526" s="1"/>
@@ -17000,7 +17000,7 @@
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="2"/>
-      <c r="D527" s="33"/>
+      <c r="D527" s="18"/>
       <c r="E527" s="3"/>
       <c r="F527" s="3"/>
       <c r="G527" s="1"/>
@@ -17029,7 +17029,7 @@
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="2"/>
-      <c r="D528" s="33"/>
+      <c r="D528" s="18"/>
       <c r="E528" s="3"/>
       <c r="F528" s="3"/>
       <c r="G528" s="1"/>
@@ -17058,7 +17058,7 @@
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="2"/>
-      <c r="D529" s="33"/>
+      <c r="D529" s="18"/>
       <c r="E529" s="3"/>
       <c r="F529" s="3"/>
       <c r="G529" s="1"/>
@@ -17087,7 +17087,7 @@
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="2"/>
-      <c r="D530" s="33"/>
+      <c r="D530" s="18"/>
       <c r="E530" s="3"/>
       <c r="F530" s="3"/>
       <c r="G530" s="1"/>
@@ -17116,7 +17116,7 @@
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="2"/>
-      <c r="D531" s="33"/>
+      <c r="D531" s="18"/>
       <c r="E531" s="3"/>
       <c r="F531" s="3"/>
       <c r="G531" s="1"/>
@@ -17145,7 +17145,7 @@
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="2"/>
-      <c r="D532" s="33"/>
+      <c r="D532" s="18"/>
       <c r="E532" s="3"/>
       <c r="F532" s="3"/>
       <c r="G532" s="1"/>
@@ -17174,7 +17174,7 @@
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="2"/>
-      <c r="D533" s="33"/>
+      <c r="D533" s="18"/>
       <c r="E533" s="3"/>
       <c r="F533" s="3"/>
       <c r="G533" s="1"/>
@@ -17203,7 +17203,7 @@
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="2"/>
-      <c r="D534" s="33"/>
+      <c r="D534" s="18"/>
       <c r="E534" s="3"/>
       <c r="F534" s="3"/>
       <c r="G534" s="1"/>
@@ -17232,7 +17232,7 @@
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="2"/>
-      <c r="D535" s="33"/>
+      <c r="D535" s="18"/>
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="1"/>
@@ -17261,7 +17261,7 @@
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="2"/>
-      <c r="D536" s="33"/>
+      <c r="D536" s="18"/>
       <c r="E536" s="3"/>
       <c r="F536" s="3"/>
       <c r="G536" s="1"/>
@@ -17290,7 +17290,7 @@
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="2"/>
-      <c r="D537" s="33"/>
+      <c r="D537" s="18"/>
       <c r="E537" s="3"/>
       <c r="F537" s="3"/>
       <c r="G537" s="1"/>
@@ -17319,7 +17319,7 @@
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="2"/>
-      <c r="D538" s="33"/>
+      <c r="D538" s="18"/>
       <c r="E538" s="3"/>
       <c r="F538" s="3"/>
       <c r="G538" s="1"/>
@@ -17348,7 +17348,7 @@
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="2"/>
-      <c r="D539" s="33"/>
+      <c r="D539" s="18"/>
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
       <c r="G539" s="1"/>
@@ -17377,7 +17377,7 @@
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="2"/>
-      <c r="D540" s="33"/>
+      <c r="D540" s="18"/>
       <c r="E540" s="3"/>
       <c r="F540" s="3"/>
       <c r="G540" s="1"/>
@@ -17406,7 +17406,7 @@
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="2"/>
-      <c r="D541" s="33"/>
+      <c r="D541" s="18"/>
       <c r="E541" s="3"/>
       <c r="F541" s="3"/>
       <c r="G541" s="1"/>
@@ -17435,7 +17435,7 @@
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="2"/>
-      <c r="D542" s="33"/>
+      <c r="D542" s="18"/>
       <c r="E542" s="3"/>
       <c r="F542" s="3"/>
       <c r="G542" s="1"/>
@@ -17464,7 +17464,7 @@
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="2"/>
-      <c r="D543" s="33"/>
+      <c r="D543" s="18"/>
       <c r="E543" s="3"/>
       <c r="F543" s="3"/>
       <c r="G543" s="1"/>
@@ -17493,7 +17493,7 @@
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="2"/>
-      <c r="D544" s="33"/>
+      <c r="D544" s="18"/>
       <c r="E544" s="3"/>
       <c r="F544" s="3"/>
       <c r="G544" s="1"/>
@@ -17522,7 +17522,7 @@
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="2"/>
-      <c r="D545" s="33"/>
+      <c r="D545" s="18"/>
       <c r="E545" s="3"/>
       <c r="F545" s="3"/>
       <c r="G545" s="1"/>
@@ -17551,7 +17551,7 @@
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="2"/>
-      <c r="D546" s="33"/>
+      <c r="D546" s="18"/>
       <c r="E546" s="3"/>
       <c r="F546" s="3"/>
       <c r="G546" s="1"/>
@@ -17580,7 +17580,7 @@
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="2"/>
-      <c r="D547" s="33"/>
+      <c r="D547" s="18"/>
       <c r="E547" s="3"/>
       <c r="F547" s="3"/>
       <c r="G547" s="1"/>
@@ -17609,7 +17609,7 @@
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="2"/>
-      <c r="D548" s="33"/>
+      <c r="D548" s="18"/>
       <c r="E548" s="3"/>
       <c r="F548" s="3"/>
       <c r="G548" s="1"/>
@@ -17638,7 +17638,7 @@
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="2"/>
-      <c r="D549" s="33"/>
+      <c r="D549" s="18"/>
       <c r="E549" s="3"/>
       <c r="F549" s="3"/>
       <c r="G549" s="1"/>
@@ -17667,7 +17667,7 @@
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="2"/>
-      <c r="D550" s="33"/>
+      <c r="D550" s="18"/>
       <c r="E550" s="3"/>
       <c r="F550" s="3"/>
       <c r="G550" s="1"/>
@@ -17696,7 +17696,7 @@
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="2"/>
-      <c r="D551" s="33"/>
+      <c r="D551" s="18"/>
       <c r="E551" s="3"/>
       <c r="F551" s="3"/>
       <c r="G551" s="1"/>
@@ -17725,7 +17725,7 @@
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="2"/>
-      <c r="D552" s="33"/>
+      <c r="D552" s="18"/>
       <c r="E552" s="3"/>
       <c r="F552" s="3"/>
       <c r="G552" s="1"/>
@@ -17754,7 +17754,7 @@
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="2"/>
-      <c r="D553" s="33"/>
+      <c r="D553" s="18"/>
       <c r="E553" s="3"/>
       <c r="F553" s="3"/>
       <c r="G553" s="1"/>
@@ -17783,7 +17783,7 @@
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="2"/>
-      <c r="D554" s="33"/>
+      <c r="D554" s="18"/>
       <c r="E554" s="3"/>
       <c r="F554" s="3"/>
       <c r="G554" s="1"/>
@@ -17812,7 +17812,7 @@
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="2"/>
-      <c r="D555" s="33"/>
+      <c r="D555" s="18"/>
       <c r="E555" s="3"/>
       <c r="F555" s="3"/>
       <c r="G555" s="1"/>
@@ -17841,7 +17841,7 @@
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="2"/>
-      <c r="D556" s="33"/>
+      <c r="D556" s="18"/>
       <c r="E556" s="3"/>
       <c r="F556" s="3"/>
       <c r="G556" s="1"/>
@@ -17870,7 +17870,7 @@
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="2"/>
-      <c r="D557" s="33"/>
+      <c r="D557" s="18"/>
       <c r="E557" s="3"/>
       <c r="F557" s="3"/>
       <c r="G557" s="1"/>
@@ -17899,7 +17899,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="2"/>
-      <c r="D558" s="33"/>
+      <c r="D558" s="18"/>
       <c r="E558" s="3"/>
       <c r="F558" s="3"/>
       <c r="G558" s="1"/>
@@ -17928,7 +17928,7 @@
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="2"/>
-      <c r="D559" s="33"/>
+      <c r="D559" s="18"/>
       <c r="E559" s="3"/>
       <c r="F559" s="3"/>
       <c r="G559" s="1"/>
@@ -17957,7 +17957,7 @@
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="2"/>
-      <c r="D560" s="33"/>
+      <c r="D560" s="18"/>
       <c r="E560" s="3"/>
       <c r="F560" s="3"/>
       <c r="G560" s="1"/>
@@ -17986,7 +17986,7 @@
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="2"/>
-      <c r="D561" s="33"/>
+      <c r="D561" s="18"/>
       <c r="E561" s="3"/>
       <c r="F561" s="3"/>
       <c r="G561" s="1"/>
@@ -18015,7 +18015,7 @@
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="2"/>
-      <c r="D562" s="33"/>
+      <c r="D562" s="18"/>
       <c r="E562" s="3"/>
       <c r="F562" s="3"/>
       <c r="G562" s="1"/>
@@ -18044,7 +18044,7 @@
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="2"/>
-      <c r="D563" s="33"/>
+      <c r="D563" s="18"/>
       <c r="E563" s="3"/>
       <c r="F563" s="3"/>
       <c r="G563" s="1"/>
@@ -18073,7 +18073,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="2"/>
-      <c r="D564" s="33"/>
+      <c r="D564" s="18"/>
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="1"/>
@@ -18102,7 +18102,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="2"/>
-      <c r="D565" s="33"/>
+      <c r="D565" s="18"/>
       <c r="E565" s="3"/>
       <c r="F565" s="3"/>
       <c r="G565" s="1"/>
@@ -18131,7 +18131,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="2"/>
-      <c r="D566" s="33"/>
+      <c r="D566" s="18"/>
       <c r="E566" s="3"/>
       <c r="F566" s="3"/>
       <c r="G566" s="1"/>
@@ -18160,7 +18160,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="2"/>
-      <c r="D567" s="33"/>
+      <c r="D567" s="18"/>
       <c r="E567" s="3"/>
       <c r="F567" s="3"/>
       <c r="G567" s="1"/>
@@ -18189,7 +18189,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="2"/>
-      <c r="D568" s="33"/>
+      <c r="D568" s="18"/>
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
       <c r="G568" s="1"/>
@@ -18218,7 +18218,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="2"/>
-      <c r="D569" s="33"/>
+      <c r="D569" s="18"/>
       <c r="E569" s="3"/>
       <c r="F569" s="3"/>
       <c r="G569" s="1"/>
@@ -18247,7 +18247,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="2"/>
-      <c r="D570" s="33"/>
+      <c r="D570" s="18"/>
       <c r="E570" s="3"/>
       <c r="F570" s="3"/>
       <c r="G570" s="1"/>
@@ -18276,7 +18276,7 @@
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="2"/>
-      <c r="D571" s="33"/>
+      <c r="D571" s="18"/>
       <c r="E571" s="3"/>
       <c r="F571" s="3"/>
       <c r="G571" s="1"/>
@@ -18305,7 +18305,7 @@
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="2"/>
-      <c r="D572" s="33"/>
+      <c r="D572" s="18"/>
       <c r="E572" s="3"/>
       <c r="F572" s="3"/>
       <c r="G572" s="1"/>
@@ -18334,7 +18334,7 @@
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="2"/>
-      <c r="D573" s="33"/>
+      <c r="D573" s="18"/>
       <c r="E573" s="3"/>
       <c r="F573" s="3"/>
       <c r="G573" s="1"/>
@@ -18363,7 +18363,7 @@
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="2"/>
-      <c r="D574" s="33"/>
+      <c r="D574" s="18"/>
       <c r="E574" s="3"/>
       <c r="F574" s="3"/>
       <c r="G574" s="1"/>
@@ -18392,7 +18392,7 @@
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="2"/>
-      <c r="D575" s="33"/>
+      <c r="D575" s="18"/>
       <c r="E575" s="3"/>
       <c r="F575" s="3"/>
       <c r="G575" s="1"/>
@@ -18421,7 +18421,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="2"/>
-      <c r="D576" s="33"/>
+      <c r="D576" s="18"/>
       <c r="E576" s="3"/>
       <c r="F576" s="3"/>
       <c r="G576" s="1"/>
@@ -18450,7 +18450,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="2"/>
-      <c r="D577" s="33"/>
+      <c r="D577" s="18"/>
       <c r="E577" s="3"/>
       <c r="F577" s="3"/>
       <c r="G577" s="1"/>
@@ -18479,7 +18479,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="2"/>
-      <c r="D578" s="33"/>
+      <c r="D578" s="18"/>
       <c r="E578" s="3"/>
       <c r="F578" s="3"/>
       <c r="G578" s="1"/>
@@ -18508,7 +18508,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="2"/>
-      <c r="D579" s="33"/>
+      <c r="D579" s="18"/>
       <c r="E579" s="3"/>
       <c r="F579" s="3"/>
       <c r="G579" s="1"/>
@@ -18537,7 +18537,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="2"/>
-      <c r="D580" s="33"/>
+      <c r="D580" s="18"/>
       <c r="E580" s="3"/>
       <c r="F580" s="3"/>
       <c r="G580" s="1"/>
@@ -18566,7 +18566,7 @@
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="2"/>
-      <c r="D581" s="33"/>
+      <c r="D581" s="18"/>
       <c r="E581" s="3"/>
       <c r="F581" s="3"/>
       <c r="G581" s="1"/>
@@ -18595,7 +18595,7 @@
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="2"/>
-      <c r="D582" s="33"/>
+      <c r="D582" s="18"/>
       <c r="E582" s="3"/>
       <c r="F582" s="3"/>
       <c r="G582" s="1"/>
@@ -18624,7 +18624,7 @@
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="2"/>
-      <c r="D583" s="33"/>
+      <c r="D583" s="18"/>
       <c r="E583" s="3"/>
       <c r="F583" s="3"/>
       <c r="G583" s="1"/>
@@ -18653,7 +18653,7 @@
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="2"/>
-      <c r="D584" s="33"/>
+      <c r="D584" s="18"/>
       <c r="E584" s="3"/>
       <c r="F584" s="3"/>
       <c r="G584" s="1"/>
@@ -18682,7 +18682,7 @@
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="2"/>
-      <c r="D585" s="33"/>
+      <c r="D585" s="18"/>
       <c r="E585" s="3"/>
       <c r="F585" s="3"/>
       <c r="G585" s="1"/>
@@ -18711,7 +18711,7 @@
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="2"/>
-      <c r="D586" s="33"/>
+      <c r="D586" s="18"/>
       <c r="E586" s="3"/>
       <c r="F586" s="3"/>
       <c r="G586" s="1"/>
@@ -18740,7 +18740,7 @@
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="2"/>
-      <c r="D587" s="33"/>
+      <c r="D587" s="18"/>
       <c r="E587" s="3"/>
       <c r="F587" s="3"/>
       <c r="G587" s="1"/>
@@ -18769,7 +18769,7 @@
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="2"/>
-      <c r="D588" s="33"/>
+      <c r="D588" s="18"/>
       <c r="E588" s="3"/>
       <c r="F588" s="3"/>
       <c r="G588" s="1"/>
@@ -18798,7 +18798,7 @@
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="2"/>
-      <c r="D589" s="33"/>
+      <c r="D589" s="18"/>
       <c r="E589" s="3"/>
       <c r="F589" s="3"/>
       <c r="G589" s="1"/>
@@ -18827,7 +18827,7 @@
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="2"/>
-      <c r="D590" s="33"/>
+      <c r="D590" s="18"/>
       <c r="E590" s="3"/>
       <c r="F590" s="3"/>
       <c r="G590" s="1"/>
@@ -18856,7 +18856,7 @@
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="2"/>
-      <c r="D591" s="33"/>
+      <c r="D591" s="18"/>
       <c r="E591" s="3"/>
       <c r="F591" s="3"/>
       <c r="G591" s="1"/>
@@ -18885,7 +18885,7 @@
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="2"/>
-      <c r="D592" s="33"/>
+      <c r="D592" s="18"/>
       <c r="E592" s="3"/>
       <c r="F592" s="3"/>
       <c r="G592" s="1"/>
@@ -18914,7 +18914,7 @@
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="2"/>
-      <c r="D593" s="33"/>
+      <c r="D593" s="18"/>
       <c r="E593" s="3"/>
       <c r="F593" s="3"/>
       <c r="G593" s="1"/>
@@ -18943,7 +18943,7 @@
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="2"/>
-      <c r="D594" s="33"/>
+      <c r="D594" s="18"/>
       <c r="E594" s="3"/>
       <c r="F594" s="3"/>
       <c r="G594" s="1"/>
@@ -18972,7 +18972,7 @@
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="2"/>
-      <c r="D595" s="33"/>
+      <c r="D595" s="18"/>
       <c r="E595" s="3"/>
       <c r="F595" s="3"/>
       <c r="G595" s="1"/>
@@ -19001,7 +19001,7 @@
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="2"/>
-      <c r="D596" s="33"/>
+      <c r="D596" s="18"/>
       <c r="E596" s="3"/>
       <c r="F596" s="3"/>
       <c r="G596" s="1"/>
@@ -19030,7 +19030,7 @@
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="2"/>
-      <c r="D597" s="33"/>
+      <c r="D597" s="18"/>
       <c r="E597" s="3"/>
       <c r="F597" s="3"/>
       <c r="G597" s="1"/>
@@ -19059,7 +19059,7 @@
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="2"/>
-      <c r="D598" s="33"/>
+      <c r="D598" s="18"/>
       <c r="E598" s="3"/>
       <c r="F598" s="3"/>
       <c r="G598" s="1"/>
@@ -19088,7 +19088,7 @@
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="2"/>
-      <c r="D599" s="33"/>
+      <c r="D599" s="18"/>
       <c r="E599" s="3"/>
       <c r="F599" s="3"/>
       <c r="G599" s="1"/>
@@ -19117,7 +19117,7 @@
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="2"/>
-      <c r="D600" s="33"/>
+      <c r="D600" s="18"/>
       <c r="E600" s="3"/>
       <c r="F600" s="3"/>
       <c r="G600" s="1"/>
@@ -19146,7 +19146,7 @@
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="2"/>
-      <c r="D601" s="33"/>
+      <c r="D601" s="18"/>
       <c r="E601" s="3"/>
       <c r="F601" s="3"/>
       <c r="G601" s="1"/>
@@ -19175,7 +19175,7 @@
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="2"/>
-      <c r="D602" s="33"/>
+      <c r="D602" s="18"/>
       <c r="E602" s="3"/>
       <c r="F602" s="3"/>
       <c r="G602" s="1"/>
@@ -19204,7 +19204,7 @@
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="2"/>
-      <c r="D603" s="33"/>
+      <c r="D603" s="18"/>
       <c r="E603" s="3"/>
       <c r="F603" s="3"/>
       <c r="G603" s="1"/>
@@ -19233,7 +19233,7 @@
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="2"/>
-      <c r="D604" s="33"/>
+      <c r="D604" s="18"/>
       <c r="E604" s="3"/>
       <c r="F604" s="3"/>
       <c r="G604" s="1"/>
@@ -19262,7 +19262,7 @@
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="2"/>
-      <c r="D605" s="33"/>
+      <c r="D605" s="18"/>
       <c r="E605" s="3"/>
       <c r="F605" s="3"/>
       <c r="G605" s="1"/>
@@ -19291,7 +19291,7 @@
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="2"/>
-      <c r="D606" s="33"/>
+      <c r="D606" s="18"/>
       <c r="E606" s="3"/>
       <c r="F606" s="3"/>
       <c r="G606" s="1"/>
@@ -19320,7 +19320,7 @@
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="2"/>
-      <c r="D607" s="33"/>
+      <c r="D607" s="18"/>
       <c r="E607" s="3"/>
       <c r="F607" s="3"/>
       <c r="G607" s="1"/>
@@ -19349,7 +19349,7 @@
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="2"/>
-      <c r="D608" s="33"/>
+      <c r="D608" s="18"/>
       <c r="E608" s="3"/>
       <c r="F608" s="3"/>
       <c r="G608" s="1"/>
@@ -19378,7 +19378,7 @@
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="2"/>
-      <c r="D609" s="33"/>
+      <c r="D609" s="18"/>
       <c r="E609" s="3"/>
       <c r="F609" s="3"/>
       <c r="G609" s="1"/>
@@ -19407,7 +19407,7 @@
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="2"/>
-      <c r="D610" s="33"/>
+      <c r="D610" s="18"/>
       <c r="E610" s="3"/>
       <c r="F610" s="3"/>
       <c r="G610" s="1"/>
@@ -19436,7 +19436,7 @@
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="2"/>
-      <c r="D611" s="33"/>
+      <c r="D611" s="18"/>
       <c r="E611" s="3"/>
       <c r="F611" s="3"/>
       <c r="G611" s="1"/>
@@ -19465,7 +19465,7 @@
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="2"/>
-      <c r="D612" s="33"/>
+      <c r="D612" s="18"/>
       <c r="E612" s="3"/>
       <c r="F612" s="3"/>
       <c r="G612" s="1"/>
@@ -19494,7 +19494,7 @@
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="2"/>
-      <c r="D613" s="33"/>
+      <c r="D613" s="18"/>
       <c r="E613" s="3"/>
       <c r="F613" s="3"/>
       <c r="G613" s="1"/>
@@ -19523,7 +19523,7 @@
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="2"/>
-      <c r="D614" s="33"/>
+      <c r="D614" s="18"/>
       <c r="E614" s="3"/>
       <c r="F614" s="3"/>
       <c r="G614" s="1"/>
@@ -19552,7 +19552,7 @@
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="2"/>
-      <c r="D615" s="33"/>
+      <c r="D615" s="18"/>
       <c r="E615" s="3"/>
       <c r="F615" s="3"/>
       <c r="G615" s="1"/>
@@ -19581,7 +19581,7 @@
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="2"/>
-      <c r="D616" s="33"/>
+      <c r="D616" s="18"/>
       <c r="E616" s="3"/>
       <c r="F616" s="3"/>
       <c r="G616" s="1"/>
@@ -19610,7 +19610,7 @@
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="2"/>
-      <c r="D617" s="33"/>
+      <c r="D617" s="18"/>
       <c r="E617" s="3"/>
       <c r="F617" s="3"/>
       <c r="G617" s="1"/>
@@ -19639,7 +19639,7 @@
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="2"/>
-      <c r="D618" s="33"/>
+      <c r="D618" s="18"/>
       <c r="E618" s="3"/>
       <c r="F618" s="3"/>
       <c r="G618" s="1"/>
@@ -19668,7 +19668,7 @@
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="2"/>
-      <c r="D619" s="33"/>
+      <c r="D619" s="18"/>
       <c r="E619" s="3"/>
       <c r="F619" s="3"/>
       <c r="G619" s="1"/>
@@ -19697,7 +19697,7 @@
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="2"/>
-      <c r="D620" s="33"/>
+      <c r="D620" s="18"/>
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
       <c r="G620" s="1"/>
@@ -19726,7 +19726,7 @@
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="2"/>
-      <c r="D621" s="33"/>
+      <c r="D621" s="18"/>
       <c r="E621" s="3"/>
       <c r="F621" s="3"/>
       <c r="G621" s="1"/>
@@ -19755,7 +19755,7 @@
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="2"/>
-      <c r="D622" s="33"/>
+      <c r="D622" s="18"/>
       <c r="E622" s="3"/>
       <c r="F622" s="3"/>
       <c r="G622" s="1"/>
@@ -19784,7 +19784,7 @@
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="2"/>
-      <c r="D623" s="33"/>
+      <c r="D623" s="18"/>
       <c r="E623" s="3"/>
       <c r="F623" s="3"/>
       <c r="G623" s="1"/>
@@ -19813,7 +19813,7 @@
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="2"/>
-      <c r="D624" s="33"/>
+      <c r="D624" s="18"/>
       <c r="E624" s="3"/>
       <c r="F624" s="3"/>
       <c r="G624" s="1"/>
@@ -19842,7 +19842,7 @@
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="2"/>
-      <c r="D625" s="33"/>
+      <c r="D625" s="18"/>
       <c r="E625" s="3"/>
       <c r="F625" s="3"/>
       <c r="G625" s="1"/>
@@ -19871,7 +19871,7 @@
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="2"/>
-      <c r="D626" s="33"/>
+      <c r="D626" s="18"/>
       <c r="E626" s="3"/>
       <c r="F626" s="3"/>
       <c r="G626" s="1"/>
@@ -19900,7 +19900,7 @@
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="2"/>
-      <c r="D627" s="33"/>
+      <c r="D627" s="18"/>
       <c r="E627" s="3"/>
       <c r="F627" s="3"/>
       <c r="G627" s="1"/>
@@ -19929,7 +19929,7 @@
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="2"/>
-      <c r="D628" s="33"/>
+      <c r="D628" s="18"/>
       <c r="E628" s="3"/>
       <c r="F628" s="3"/>
       <c r="G628" s="1"/>
@@ -19958,7 +19958,7 @@
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="2"/>
-      <c r="D629" s="33"/>
+      <c r="D629" s="18"/>
       <c r="E629" s="3"/>
       <c r="F629" s="3"/>
       <c r="G629" s="1"/>
@@ -19987,7 +19987,7 @@
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="2"/>
-      <c r="D630" s="33"/>
+      <c r="D630" s="18"/>
       <c r="E630" s="3"/>
       <c r="F630" s="3"/>
       <c r="G630" s="1"/>
@@ -20016,7 +20016,7 @@
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="2"/>
-      <c r="D631" s="33"/>
+      <c r="D631" s="18"/>
       <c r="E631" s="3"/>
       <c r="F631" s="3"/>
       <c r="G631" s="1"/>
@@ -20045,7 +20045,7 @@
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="2"/>
-      <c r="D632" s="33"/>
+      <c r="D632" s="18"/>
       <c r="E632" s="3"/>
       <c r="F632" s="3"/>
       <c r="G632" s="1"/>
@@ -20074,7 +20074,7 @@
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="2"/>
-      <c r="D633" s="33"/>
+      <c r="D633" s="18"/>
       <c r="E633" s="3"/>
       <c r="F633" s="3"/>
       <c r="G633" s="1"/>
@@ -20103,7 +20103,7 @@
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="2"/>
-      <c r="D634" s="33"/>
+      <c r="D634" s="18"/>
       <c r="E634" s="3"/>
       <c r="F634" s="3"/>
       <c r="G634" s="1"/>
@@ -20132,7 +20132,7 @@
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="2"/>
-      <c r="D635" s="33"/>
+      <c r="D635" s="18"/>
       <c r="E635" s="3"/>
       <c r="F635" s="3"/>
       <c r="G635" s="1"/>
@@ -20161,7 +20161,7 @@
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="2"/>
-      <c r="D636" s="33"/>
+      <c r="D636" s="18"/>
       <c r="E636" s="3"/>
       <c r="F636" s="3"/>
       <c r="G636" s="1"/>
@@ -20190,7 +20190,7 @@
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="2"/>
-      <c r="D637" s="33"/>
+      <c r="D637" s="18"/>
       <c r="E637" s="3"/>
       <c r="F637" s="3"/>
       <c r="G637" s="1"/>
@@ -20219,7 +20219,7 @@
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="2"/>
-      <c r="D638" s="33"/>
+      <c r="D638" s="18"/>
       <c r="E638" s="3"/>
       <c r="F638" s="3"/>
       <c r="G638" s="1"/>
@@ -20248,7 +20248,7 @@
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="2"/>
-      <c r="D639" s="33"/>
+      <c r="D639" s="18"/>
       <c r="E639" s="3"/>
       <c r="F639" s="3"/>
       <c r="G639" s="1"/>
@@ -20277,7 +20277,7 @@
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="2"/>
-      <c r="D640" s="33"/>
+      <c r="D640" s="18"/>
       <c r="E640" s="3"/>
       <c r="F640" s="3"/>
       <c r="G640" s="1"/>
@@ -20306,7 +20306,7 @@
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="2"/>
-      <c r="D641" s="33"/>
+      <c r="D641" s="18"/>
       <c r="E641" s="3"/>
       <c r="F641" s="3"/>
       <c r="G641" s="1"/>
@@ -20335,7 +20335,7 @@
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="2"/>
-      <c r="D642" s="33"/>
+      <c r="D642" s="18"/>
       <c r="E642" s="3"/>
       <c r="F642" s="3"/>
       <c r="G642" s="1"/>
@@ -20364,7 +20364,7 @@
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="2"/>
-      <c r="D643" s="33"/>
+      <c r="D643" s="18"/>
       <c r="E643" s="3"/>
       <c r="F643" s="3"/>
       <c r="G643" s="1"/>
@@ -20393,7 +20393,7 @@
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="2"/>
-      <c r="D644" s="33"/>
+      <c r="D644" s="18"/>
       <c r="E644" s="3"/>
       <c r="F644" s="3"/>
       <c r="G644" s="1"/>
@@ -20422,7 +20422,7 @@
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="2"/>
-      <c r="D645" s="33"/>
+      <c r="D645" s="18"/>
       <c r="E645" s="3"/>
       <c r="F645" s="3"/>
       <c r="G645" s="1"/>
@@ -20451,7 +20451,7 @@
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="2"/>
-      <c r="D646" s="33"/>
+      <c r="D646" s="18"/>
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
       <c r="G646" s="1"/>
@@ -20480,7 +20480,7 @@
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="2"/>
-      <c r="D647" s="33"/>
+      <c r="D647" s="18"/>
       <c r="E647" s="3"/>
       <c r="F647" s="3"/>
       <c r="G647" s="1"/>
@@ -20509,7 +20509,7 @@
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="2"/>
-      <c r="D648" s="33"/>
+      <c r="D648" s="18"/>
       <c r="E648" s="3"/>
       <c r="F648" s="3"/>
       <c r="G648" s="1"/>
@@ -20538,7 +20538,7 @@
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="2"/>
-      <c r="D649" s="33"/>
+      <c r="D649" s="18"/>
       <c r="E649" s="3"/>
       <c r="F649" s="3"/>
       <c r="G649" s="1"/>
@@ -20567,7 +20567,7 @@
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="2"/>
-      <c r="D650" s="33"/>
+      <c r="D650" s="18"/>
       <c r="E650" s="3"/>
       <c r="F650" s="3"/>
       <c r="G650" s="1"/>
@@ -20596,7 +20596,7 @@
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="2"/>
-      <c r="D651" s="33"/>
+      <c r="D651" s="18"/>
       <c r="E651" s="3"/>
       <c r="F651" s="3"/>
       <c r="G651" s="1"/>
@@ -20625,7 +20625,7 @@
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="2"/>
-      <c r="D652" s="33"/>
+      <c r="D652" s="18"/>
       <c r="E652" s="3"/>
       <c r="F652" s="3"/>
       <c r="G652" s="1"/>
@@ -20654,7 +20654,7 @@
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="2"/>
-      <c r="D653" s="33"/>
+      <c r="D653" s="18"/>
       <c r="E653" s="3"/>
       <c r="F653" s="3"/>
       <c r="G653" s="1"/>
@@ -20683,7 +20683,7 @@
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="2"/>
-      <c r="D654" s="33"/>
+      <c r="D654" s="18"/>
       <c r="E654" s="3"/>
       <c r="F654" s="3"/>
       <c r="G654" s="1"/>
@@ -20712,7 +20712,7 @@
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="2"/>
-      <c r="D655" s="33"/>
+      <c r="D655" s="18"/>
       <c r="E655" s="3"/>
       <c r="F655" s="3"/>
       <c r="G655" s="1"/>
@@ -20741,7 +20741,7 @@
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="2"/>
-      <c r="D656" s="33"/>
+      <c r="D656" s="18"/>
       <c r="E656" s="3"/>
       <c r="F656" s="3"/>
       <c r="G656" s="1"/>
@@ -20770,7 +20770,7 @@
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="2"/>
-      <c r="D657" s="33"/>
+      <c r="D657" s="18"/>
       <c r="E657" s="3"/>
       <c r="F657" s="3"/>
       <c r="G657" s="1"/>
@@ -20799,7 +20799,7 @@
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="2"/>
-      <c r="D658" s="33"/>
+      <c r="D658" s="18"/>
       <c r="E658" s="3"/>
       <c r="F658" s="3"/>
       <c r="G658" s="1"/>
@@ -20828,7 +20828,7 @@
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="2"/>
-      <c r="D659" s="33"/>
+      <c r="D659" s="18"/>
       <c r="E659" s="3"/>
       <c r="F659" s="3"/>
       <c r="G659" s="1"/>
@@ -20857,7 +20857,7 @@
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="2"/>
-      <c r="D660" s="33"/>
+      <c r="D660" s="18"/>
       <c r="E660" s="3"/>
       <c r="F660" s="3"/>
       <c r="G660" s="1"/>
@@ -20886,7 +20886,7 @@
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="2"/>
-      <c r="D661" s="33"/>
+      <c r="D661" s="18"/>
       <c r="E661" s="3"/>
       <c r="F661" s="3"/>
       <c r="G661" s="1"/>
@@ -20915,7 +20915,7 @@
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="2"/>
-      <c r="D662" s="33"/>
+      <c r="D662" s="18"/>
       <c r="E662" s="3"/>
       <c r="F662" s="3"/>
       <c r="G662" s="1"/>
@@ -20944,7 +20944,7 @@
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="2"/>
-      <c r="D663" s="33"/>
+      <c r="D663" s="18"/>
       <c r="E663" s="3"/>
       <c r="F663" s="3"/>
       <c r="G663" s="1"/>
@@ -20973,7 +20973,7 @@
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="2"/>
-      <c r="D664" s="33"/>
+      <c r="D664" s="18"/>
       <c r="E664" s="3"/>
       <c r="F664" s="3"/>
       <c r="G664" s="1"/>
@@ -21002,7 +21002,7 @@
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="2"/>
-      <c r="D665" s="33"/>
+      <c r="D665" s="18"/>
       <c r="E665" s="3"/>
       <c r="F665" s="3"/>
       <c r="G665" s="1"/>
@@ -21031,7 +21031,7 @@
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="2"/>
-      <c r="D666" s="33"/>
+      <c r="D666" s="18"/>
       <c r="E666" s="3"/>
       <c r="F666" s="3"/>
       <c r="G666" s="1"/>
@@ -21060,7 +21060,7 @@
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="2"/>
-      <c r="D667" s="33"/>
+      <c r="D667" s="18"/>
       <c r="E667" s="3"/>
       <c r="F667" s="3"/>
       <c r="G667" s="1"/>
@@ -21089,7 +21089,7 @@
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="2"/>
-      <c r="D668" s="33"/>
+      <c r="D668" s="18"/>
       <c r="E668" s="3"/>
       <c r="F668" s="3"/>
       <c r="G668" s="1"/>
@@ -21118,7 +21118,7 @@
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="2"/>
-      <c r="D669" s="33"/>
+      <c r="D669" s="18"/>
       <c r="E669" s="3"/>
       <c r="F669" s="3"/>
       <c r="G669" s="1"/>
@@ -21147,7 +21147,7 @@
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="2"/>
-      <c r="D670" s="33"/>
+      <c r="D670" s="18"/>
       <c r="E670" s="3"/>
       <c r="F670" s="3"/>
       <c r="G670" s="1"/>
@@ -21176,7 +21176,7 @@
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="2"/>
-      <c r="D671" s="33"/>
+      <c r="D671" s="18"/>
       <c r="E671" s="3"/>
       <c r="F671" s="3"/>
       <c r="G671" s="1"/>
@@ -21205,7 +21205,7 @@
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="2"/>
-      <c r="D672" s="33"/>
+      <c r="D672" s="18"/>
       <c r="E672" s="3"/>
       <c r="F672" s="3"/>
       <c r="G672" s="1"/>
@@ -21234,7 +21234,7 @@
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="2"/>
-      <c r="D673" s="33"/>
+      <c r="D673" s="18"/>
       <c r="E673" s="3"/>
       <c r="F673" s="3"/>
       <c r="G673" s="1"/>
@@ -21263,7 +21263,7 @@
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="2"/>
-      <c r="D674" s="33"/>
+      <c r="D674" s="18"/>
       <c r="E674" s="3"/>
       <c r="F674" s="3"/>
       <c r="G674" s="1"/>
@@ -21292,7 +21292,7 @@
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="2"/>
-      <c r="D675" s="33"/>
+      <c r="D675" s="18"/>
       <c r="E675" s="3"/>
       <c r="F675" s="3"/>
       <c r="G675" s="1"/>
@@ -21321,7 +21321,7 @@
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="2"/>
-      <c r="D676" s="33"/>
+      <c r="D676" s="18"/>
       <c r="E676" s="3"/>
       <c r="F676" s="3"/>
       <c r="G676" s="1"/>
@@ -21350,7 +21350,7 @@
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="2"/>
-      <c r="D677" s="33"/>
+      <c r="D677" s="18"/>
       <c r="E677" s="3"/>
       <c r="F677" s="3"/>
       <c r="G677" s="1"/>
@@ -21379,7 +21379,7 @@
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="2"/>
-      <c r="D678" s="33"/>
+      <c r="D678" s="18"/>
       <c r="E678" s="3"/>
       <c r="F678" s="3"/>
       <c r="G678" s="1"/>
@@ -21408,7 +21408,7 @@
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="2"/>
-      <c r="D679" s="33"/>
+      <c r="D679" s="18"/>
       <c r="E679" s="3"/>
       <c r="F679" s="3"/>
       <c r="G679" s="1"/>
@@ -21437,7 +21437,7 @@
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="2"/>
-      <c r="D680" s="33"/>
+      <c r="D680" s="18"/>
       <c r="E680" s="3"/>
       <c r="F680" s="3"/>
       <c r="G680" s="1"/>
@@ -21466,7 +21466,7 @@
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="2"/>
-      <c r="D681" s="33"/>
+      <c r="D681" s="18"/>
       <c r="E681" s="3"/>
       <c r="F681" s="3"/>
       <c r="G681" s="1"/>
@@ -21495,7 +21495,7 @@
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="2"/>
-      <c r="D682" s="33"/>
+      <c r="D682" s="18"/>
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
       <c r="G682" s="1"/>
@@ -21524,7 +21524,7 @@
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="2"/>
-      <c r="D683" s="33"/>
+      <c r="D683" s="18"/>
       <c r="E683" s="3"/>
       <c r="F683" s="3"/>
       <c r="G683" s="1"/>
@@ -21553,7 +21553,7 @@
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="2"/>
-      <c r="D684" s="33"/>
+      <c r="D684" s="18"/>
       <c r="E684" s="3"/>
       <c r="F684" s="3"/>
       <c r="G684" s="1"/>
@@ -21582,7 +21582,7 @@
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="2"/>
-      <c r="D685" s="33"/>
+      <c r="D685" s="18"/>
       <c r="E685" s="3"/>
       <c r="F685" s="3"/>
       <c r="G685" s="1"/>
@@ -21611,7 +21611,7 @@
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="2"/>
-      <c r="D686" s="33"/>
+      <c r="D686" s="18"/>
       <c r="E686" s="3"/>
       <c r="F686" s="3"/>
       <c r="G686" s="1"/>
@@ -21640,7 +21640,7 @@
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="2"/>
-      <c r="D687" s="33"/>
+      <c r="D687" s="18"/>
       <c r="E687" s="3"/>
       <c r="F687" s="3"/>
       <c r="G687" s="1"/>
@@ -21669,7 +21669,7 @@
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="2"/>
-      <c r="D688" s="33"/>
+      <c r="D688" s="18"/>
       <c r="E688" s="3"/>
       <c r="F688" s="3"/>
       <c r="G688" s="1"/>
@@ -21698,7 +21698,7 @@
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="2"/>
-      <c r="D689" s="33"/>
+      <c r="D689" s="18"/>
       <c r="E689" s="3"/>
       <c r="F689" s="3"/>
       <c r="G689" s="1"/>
@@ -21727,7 +21727,7 @@
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="2"/>
-      <c r="D690" s="33"/>
+      <c r="D690" s="18"/>
       <c r="E690" s="3"/>
       <c r="F690" s="3"/>
       <c r="G690" s="1"/>
@@ -21756,7 +21756,7 @@
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="2"/>
-      <c r="D691" s="33"/>
+      <c r="D691" s="18"/>
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
       <c r="G691" s="1"/>
@@ -21785,7 +21785,7 @@
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="2"/>
-      <c r="D692" s="33"/>
+      <c r="D692" s="18"/>
       <c r="E692" s="3"/>
       <c r="F692" s="3"/>
       <c r="G692" s="1"/>
@@ -21814,7 +21814,7 @@
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="2"/>
-      <c r="D693" s="33"/>
+      <c r="D693" s="18"/>
       <c r="E693" s="3"/>
       <c r="F693" s="3"/>
       <c r="G693" s="1"/>
@@ -21843,7 +21843,7 @@
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="2"/>
-      <c r="D694" s="33"/>
+      <c r="D694" s="18"/>
       <c r="E694" s="3"/>
       <c r="F694" s="3"/>
       <c r="G694" s="1"/>
@@ -21872,7 +21872,7 @@
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="2"/>
-      <c r="D695" s="33"/>
+      <c r="D695" s="18"/>
       <c r="E695" s="3"/>
       <c r="F695" s="3"/>
       <c r="G695" s="1"/>
@@ -21901,7 +21901,7 @@
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="2"/>
-      <c r="D696" s="33"/>
+      <c r="D696" s="18"/>
       <c r="E696" s="3"/>
       <c r="F696" s="3"/>
       <c r="G696" s="1"/>
@@ -21930,7 +21930,7 @@
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="2"/>
-      <c r="D697" s="33"/>
+      <c r="D697" s="18"/>
       <c r="E697" s="3"/>
       <c r="F697" s="3"/>
       <c r="G697" s="1"/>
@@ -21959,7 +21959,7 @@
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="2"/>
-      <c r="D698" s="33"/>
+      <c r="D698" s="18"/>
       <c r="E698" s="3"/>
       <c r="F698" s="3"/>
       <c r="G698" s="1"/>
@@ -21988,7 +21988,7 @@
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="2"/>
-      <c r="D699" s="33"/>
+      <c r="D699" s="18"/>
       <c r="E699" s="3"/>
       <c r="F699" s="3"/>
       <c r="G699" s="1"/>
@@ -22017,7 +22017,7 @@
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="2"/>
-      <c r="D700" s="33"/>
+      <c r="D700" s="18"/>
       <c r="E700" s="3"/>
       <c r="F700" s="3"/>
       <c r="G700" s="1"/>
@@ -22046,7 +22046,7 @@
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="2"/>
-      <c r="D701" s="33"/>
+      <c r="D701" s="18"/>
       <c r="E701" s="3"/>
       <c r="F701" s="3"/>
       <c r="G701" s="1"/>
@@ -22075,7 +22075,7 @@
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="2"/>
-      <c r="D702" s="33"/>
+      <c r="D702" s="18"/>
       <c r="E702" s="3"/>
       <c r="F702" s="3"/>
       <c r="G702" s="1"/>
@@ -22104,7 +22104,7 @@
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="2"/>
-      <c r="D703" s="33"/>
+      <c r="D703" s="18"/>
       <c r="E703" s="3"/>
       <c r="F703" s="3"/>
       <c r="G703" s="1"/>
@@ -22133,7 +22133,7 @@
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="2"/>
-      <c r="D704" s="33"/>
+      <c r="D704" s="18"/>
       <c r="E704" s="3"/>
       <c r="F704" s="3"/>
       <c r="G704" s="1"/>
@@ -22162,7 +22162,7 @@
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="2"/>
-      <c r="D705" s="33"/>
+      <c r="D705" s="18"/>
       <c r="E705" s="3"/>
       <c r="F705" s="3"/>
       <c r="G705" s="1"/>
@@ -22191,7 +22191,7 @@
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="2"/>
-      <c r="D706" s="33"/>
+      <c r="D706" s="18"/>
       <c r="E706" s="3"/>
       <c r="F706" s="3"/>
       <c r="G706" s="1"/>
@@ -22220,7 +22220,7 @@
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="2"/>
-      <c r="D707" s="33"/>
+      <c r="D707" s="18"/>
       <c r="E707" s="3"/>
       <c r="F707" s="3"/>
       <c r="G707" s="1"/>
@@ -22249,7 +22249,7 @@
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="2"/>
-      <c r="D708" s="33"/>
+      <c r="D708" s="18"/>
       <c r="E708" s="3"/>
       <c r="F708" s="3"/>
       <c r="G708" s="1"/>
@@ -22278,7 +22278,7 @@
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="2"/>
-      <c r="D709" s="33"/>
+      <c r="D709" s="18"/>
       <c r="E709" s="3"/>
       <c r="F709" s="3"/>
       <c r="G709" s="1"/>
@@ -22307,7 +22307,7 @@
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="2"/>
-      <c r="D710" s="33"/>
+      <c r="D710" s="18"/>
       <c r="E710" s="3"/>
       <c r="F710" s="3"/>
       <c r="G710" s="1"/>
@@ -22336,7 +22336,7 @@
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="2"/>
-      <c r="D711" s="33"/>
+      <c r="D711" s="18"/>
       <c r="E711" s="3"/>
       <c r="F711" s="3"/>
       <c r="G711" s="1"/>
@@ -22365,7 +22365,7 @@
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="2"/>
-      <c r="D712" s="33"/>
+      <c r="D712" s="18"/>
       <c r="E712" s="3"/>
       <c r="F712" s="3"/>
       <c r="G712" s="1"/>
@@ -22394,7 +22394,7 @@
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="2"/>
-      <c r="D713" s="33"/>
+      <c r="D713" s="18"/>
       <c r="E713" s="3"/>
       <c r="F713" s="3"/>
       <c r="G713" s="1"/>
@@ -22423,7 +22423,7 @@
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="2"/>
-      <c r="D714" s="33"/>
+      <c r="D714" s="18"/>
       <c r="E714" s="3"/>
       <c r="F714" s="3"/>
       <c r="G714" s="1"/>
@@ -22452,7 +22452,7 @@
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="2"/>
-      <c r="D715" s="33"/>
+      <c r="D715" s="18"/>
       <c r="E715" s="3"/>
       <c r="F715" s="3"/>
       <c r="G715" s="1"/>
@@ -22481,7 +22481,7 @@
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="2"/>
-      <c r="D716" s="33"/>
+      <c r="D716" s="18"/>
       <c r="E716" s="3"/>
       <c r="F716" s="3"/>
       <c r="G716" s="1"/>
@@ -22510,7 +22510,7 @@
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="2"/>
-      <c r="D717" s="33"/>
+      <c r="D717" s="18"/>
       <c r="E717" s="3"/>
       <c r="F717" s="3"/>
       <c r="G717" s="1"/>
@@ -22539,7 +22539,7 @@
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="2"/>
-      <c r="D718" s="33"/>
+      <c r="D718" s="18"/>
       <c r="E718" s="3"/>
       <c r="F718" s="3"/>
       <c r="G718" s="1"/>
@@ -22568,7 +22568,7 @@
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="2"/>
-      <c r="D719" s="33"/>
+      <c r="D719" s="18"/>
       <c r="E719" s="3"/>
       <c r="F719" s="3"/>
       <c r="G719" s="1"/>
@@ -22597,7 +22597,7 @@
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="2"/>
-      <c r="D720" s="33"/>
+      <c r="D720" s="18"/>
       <c r="E720" s="3"/>
       <c r="F720" s="3"/>
       <c r="G720" s="1"/>
@@ -22626,7 +22626,7 @@
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="2"/>
-      <c r="D721" s="33"/>
+      <c r="D721" s="18"/>
       <c r="E721" s="3"/>
       <c r="F721" s="3"/>
       <c r="G721" s="1"/>
@@ -22655,7 +22655,7 @@
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="2"/>
-      <c r="D722" s="33"/>
+      <c r="D722" s="18"/>
       <c r="E722" s="3"/>
       <c r="F722" s="3"/>
       <c r="G722" s="1"/>
@@ -22684,7 +22684,7 @@
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="2"/>
-      <c r="D723" s="33"/>
+      <c r="D723" s="18"/>
       <c r="E723" s="3"/>
       <c r="F723" s="3"/>
       <c r="G723" s="1"/>
@@ -22713,7 +22713,7 @@
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="2"/>
-      <c r="D724" s="33"/>
+      <c r="D724" s="18"/>
       <c r="E724" s="3"/>
       <c r="F724" s="3"/>
       <c r="G724" s="1"/>
@@ -22742,7 +22742,7 @@
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="2"/>
-      <c r="D725" s="33"/>
+      <c r="D725" s="18"/>
       <c r="E725" s="3"/>
       <c r="F725" s="3"/>
       <c r="G725" s="1"/>
@@ -22771,7 +22771,7 @@
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="2"/>
-      <c r="D726" s="33"/>
+      <c r="D726" s="18"/>
       <c r="E726" s="3"/>
       <c r="F726" s="3"/>
       <c r="G726" s="1"/>
@@ -22800,7 +22800,7 @@
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="2"/>
-      <c r="D727" s="33"/>
+      <c r="D727" s="18"/>
       <c r="E727" s="3"/>
       <c r="F727" s="3"/>
       <c r="G727" s="1"/>
@@ -22829,7 +22829,7 @@
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="2"/>
-      <c r="D728" s="33"/>
+      <c r="D728" s="18"/>
       <c r="E728" s="3"/>
       <c r="F728" s="3"/>
       <c r="G728" s="1"/>
@@ -22858,7 +22858,7 @@
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="2"/>
-      <c r="D729" s="33"/>
+      <c r="D729" s="18"/>
       <c r="E729" s="3"/>
       <c r="F729" s="3"/>
       <c r="G729" s="1"/>
@@ -22887,7 +22887,7 @@
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="2"/>
-      <c r="D730" s="33"/>
+      <c r="D730" s="18"/>
       <c r="E730" s="3"/>
       <c r="F730" s="3"/>
       <c r="G730" s="1"/>
@@ -22916,7 +22916,7 @@
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="2"/>
-      <c r="D731" s="33"/>
+      <c r="D731" s="18"/>
       <c r="E731" s="3"/>
       <c r="F731" s="3"/>
       <c r="G731" s="1"/>
@@ -22945,7 +22945,7 @@
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="2"/>
-      <c r="D732" s="33"/>
+      <c r="D732" s="18"/>
       <c r="E732" s="3"/>
       <c r="F732" s="3"/>
       <c r="G732" s="1"/>
@@ -22974,7 +22974,7 @@
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="2"/>
-      <c r="D733" s="33"/>
+      <c r="D733" s="18"/>
       <c r="E733" s="3"/>
       <c r="F733" s="3"/>
       <c r="G733" s="1"/>
@@ -23003,7 +23003,7 @@
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="2"/>
-      <c r="D734" s="33"/>
+      <c r="D734" s="18"/>
       <c r="E734" s="3"/>
       <c r="F734" s="3"/>
       <c r="G734" s="1"/>
@@ -23032,7 +23032,7 @@
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="2"/>
-      <c r="D735" s="33"/>
+      <c r="D735" s="18"/>
       <c r="E735" s="3"/>
       <c r="F735" s="3"/>
       <c r="G735" s="1"/>
@@ -23061,7 +23061,7 @@
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="2"/>
-      <c r="D736" s="33"/>
+      <c r="D736" s="18"/>
       <c r="E736" s="3"/>
       <c r="F736" s="3"/>
       <c r="G736" s="1"/>
@@ -23090,7 +23090,7 @@
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="2"/>
-      <c r="D737" s="33"/>
+      <c r="D737" s="18"/>
       <c r="E737" s="3"/>
       <c r="F737" s="3"/>
       <c r="G737" s="1"/>
@@ -23119,7 +23119,7 @@
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="2"/>
-      <c r="D738" s="33"/>
+      <c r="D738" s="18"/>
       <c r="E738" s="3"/>
       <c r="F738" s="3"/>
       <c r="G738" s="1"/>
@@ -23148,7 +23148,7 @@
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="2"/>
-      <c r="D739" s="33"/>
+      <c r="D739" s="18"/>
       <c r="E739" s="3"/>
       <c r="F739" s="3"/>
       <c r="G739" s="1"/>
@@ -23177,7 +23177,7 @@
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="2"/>
-      <c r="D740" s="33"/>
+      <c r="D740" s="18"/>
       <c r="E740" s="3"/>
       <c r="F740" s="3"/>
       <c r="G740" s="1"/>
@@ -23206,7 +23206,7 @@
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="2"/>
-      <c r="D741" s="33"/>
+      <c r="D741" s="18"/>
       <c r="E741" s="3"/>
       <c r="F741" s="3"/>
       <c r="G741" s="1"/>
@@ -23235,7 +23235,7 @@
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="2"/>
-      <c r="D742" s="33"/>
+      <c r="D742" s="18"/>
       <c r="E742" s="3"/>
       <c r="F742" s="3"/>
       <c r="G742" s="1"/>
@@ -23264,7 +23264,7 @@
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="2"/>
-      <c r="D743" s="33"/>
+      <c r="D743" s="18"/>
       <c r="E743" s="3"/>
       <c r="F743" s="3"/>
       <c r="G743" s="1"/>
@@ -23293,7 +23293,7 @@
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="2"/>
-      <c r="D744" s="33"/>
+      <c r="D744" s="18"/>
       <c r="E744" s="3"/>
       <c r="F744" s="3"/>
       <c r="G744" s="1"/>
@@ -23322,7 +23322,7 @@
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="2"/>
-      <c r="D745" s="33"/>
+      <c r="D745" s="18"/>
       <c r="E745" s="3"/>
       <c r="F745" s="3"/>
       <c r="G745" s="1"/>
@@ -23351,7 +23351,7 @@
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="2"/>
-      <c r="D746" s="33"/>
+      <c r="D746" s="18"/>
       <c r="E746" s="3"/>
       <c r="F746" s="3"/>
       <c r="G746" s="1"/>
@@ -23380,7 +23380,7 @@
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="2"/>
-      <c r="D747" s="33"/>
+      <c r="D747" s="18"/>
       <c r="E747" s="3"/>
       <c r="F747" s="3"/>
       <c r="G747" s="1"/>
@@ -23409,7 +23409,7 @@
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="2"/>
-      <c r="D748" s="33"/>
+      <c r="D748" s="18"/>
       <c r="E748" s="3"/>
       <c r="F748" s="3"/>
       <c r="G748" s="1"/>
@@ -23438,7 +23438,7 @@
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="2"/>
-      <c r="D749" s="33"/>
+      <c r="D749" s="18"/>
       <c r="E749" s="3"/>
       <c r="F749" s="3"/>
       <c r="G749" s="1"/>
@@ -23467,7 +23467,7 @@
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="2"/>
-      <c r="D750" s="33"/>
+      <c r="D750" s="18"/>
       <c r="E750" s="3"/>
       <c r="F750" s="3"/>
       <c r="G750" s="1"/>
@@ -23496,7 +23496,7 @@
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="2"/>
-      <c r="D751" s="33"/>
+      <c r="D751" s="18"/>
       <c r="E751" s="3"/>
       <c r="F751" s="3"/>
       <c r="G751" s="1"/>
@@ -23525,7 +23525,7 @@
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="2"/>
-      <c r="D752" s="33"/>
+      <c r="D752" s="18"/>
       <c r="E752" s="3"/>
       <c r="F752" s="3"/>
       <c r="G752" s="1"/>
@@ -23554,7 +23554,7 @@
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="2"/>
-      <c r="D753" s="33"/>
+      <c r="D753" s="18"/>
       <c r="E753" s="3"/>
       <c r="F753" s="3"/>
       <c r="G753" s="1"/>
@@ -23583,7 +23583,7 @@
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="2"/>
-      <c r="D754" s="33"/>
+      <c r="D754" s="18"/>
       <c r="E754" s="3"/>
       <c r="F754" s="3"/>
       <c r="G754" s="1"/>
@@ -23612,7 +23612,7 @@
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="2"/>
-      <c r="D755" s="33"/>
+      <c r="D755" s="18"/>
       <c r="E755" s="3"/>
       <c r="F755" s="3"/>
       <c r="G755" s="1"/>
@@ -23641,7 +23641,7 @@
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="2"/>
-      <c r="D756" s="33"/>
+      <c r="D756" s="18"/>
       <c r="E756" s="3"/>
       <c r="F756" s="3"/>
       <c r="G756" s="1"/>
@@ -23670,7 +23670,7 @@
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="2"/>
-      <c r="D757" s="33"/>
+      <c r="D757" s="18"/>
       <c r="E757" s="3"/>
       <c r="F757" s="3"/>
       <c r="G757" s="1"/>
@@ -23699,7 +23699,7 @@
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="2"/>
-      <c r="D758" s="33"/>
+      <c r="D758" s="18"/>
       <c r="E758" s="3"/>
       <c r="F758" s="3"/>
       <c r="G758" s="1"/>
@@ -23728,7 +23728,7 @@
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="2"/>
-      <c r="D759" s="33"/>
+      <c r="D759" s="18"/>
       <c r="E759" s="3"/>
       <c r="F759" s="3"/>
       <c r="G759" s="1"/>
@@ -23757,7 +23757,7 @@
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="2"/>
-      <c r="D760" s="33"/>
+      <c r="D760" s="18"/>
       <c r="E760" s="3"/>
       <c r="F760" s="3"/>
       <c r="G760" s="1"/>
@@ -23786,7 +23786,7 @@
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="2"/>
-      <c r="D761" s="33"/>
+      <c r="D761" s="18"/>
       <c r="E761" s="3"/>
       <c r="F761" s="3"/>
       <c r="G761" s="1"/>
@@ -23815,7 +23815,7 @@
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="2"/>
-      <c r="D762" s="33"/>
+      <c r="D762" s="18"/>
       <c r="E762" s="3"/>
       <c r="F762" s="3"/>
       <c r="G762" s="1"/>
@@ -23844,7 +23844,7 @@
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="2"/>
-      <c r="D763" s="33"/>
+      <c r="D763" s="18"/>
       <c r="E763" s="3"/>
       <c r="F763" s="3"/>
       <c r="G763" s="1"/>
@@ -23873,7 +23873,7 @@
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="2"/>
-      <c r="D764" s="33"/>
+      <c r="D764" s="18"/>
       <c r="E764" s="3"/>
       <c r="F764" s="3"/>
       <c r="G764" s="1"/>
@@ -23902,7 +23902,7 @@
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="2"/>
-      <c r="D765" s="33"/>
+      <c r="D765" s="18"/>
       <c r="E765" s="3"/>
       <c r="F765" s="3"/>
       <c r="G765" s="1"/>
@@ -23931,7 +23931,7 @@
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="2"/>
-      <c r="D766" s="33"/>
+      <c r="D766" s="18"/>
       <c r="E766" s="3"/>
       <c r="F766" s="3"/>
       <c r="G766" s="1"/>
@@ -23960,7 +23960,7 @@
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="2"/>
-      <c r="D767" s="33"/>
+      <c r="D767" s="18"/>
       <c r="E767" s="3"/>
       <c r="F767" s="3"/>
       <c r="G767" s="1"/>
@@ -23989,7 +23989,7 @@
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="2"/>
-      <c r="D768" s="33"/>
+      <c r="D768" s="18"/>
       <c r="E768" s="3"/>
       <c r="F768" s="3"/>
       <c r="G768" s="1"/>
@@ -24018,7 +24018,7 @@
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="2"/>
-      <c r="D769" s="33"/>
+      <c r="D769" s="18"/>
       <c r="E769" s="3"/>
       <c r="F769" s="3"/>
       <c r="G769" s="1"/>
@@ -24047,7 +24047,7 @@
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="2"/>
-      <c r="D770" s="33"/>
+      <c r="D770" s="18"/>
       <c r="E770" s="3"/>
       <c r="F770" s="3"/>
       <c r="G770" s="1"/>
@@ -24076,7 +24076,7 @@
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="2"/>
-      <c r="D771" s="33"/>
+      <c r="D771" s="18"/>
       <c r="E771" s="3"/>
       <c r="F771" s="3"/>
       <c r="G771" s="1"/>
@@ -24105,7 +24105,7 @@
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="2"/>
-      <c r="D772" s="33"/>
+      <c r="D772" s="18"/>
       <c r="E772" s="3"/>
       <c r="F772" s="3"/>
       <c r="G772" s="1"/>
@@ -24134,7 +24134,7 @@
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="2"/>
-      <c r="D773" s="33"/>
+      <c r="D773" s="18"/>
       <c r="E773" s="3"/>
       <c r="F773" s="3"/>
       <c r="G773" s="1"/>
@@ -24163,7 +24163,7 @@
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="2"/>
-      <c r="D774" s="33"/>
+      <c r="D774" s="18"/>
       <c r="E774" s="3"/>
       <c r="F774" s="3"/>
       <c r="G774" s="1"/>
@@ -24192,7 +24192,7 @@
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="2"/>
-      <c r="D775" s="33"/>
+      <c r="D775" s="18"/>
       <c r="E775" s="3"/>
       <c r="F775" s="3"/>
       <c r="G775" s="1"/>
@@ -24221,7 +24221,7 @@
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="2"/>
-      <c r="D776" s="33"/>
+      <c r="D776" s="18"/>
       <c r="E776" s="3"/>
       <c r="F776" s="3"/>
       <c r="G776" s="1"/>
@@ -24250,7 +24250,7 @@
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="2"/>
-      <c r="D777" s="33"/>
+      <c r="D777" s="18"/>
       <c r="E777" s="3"/>
       <c r="F777" s="3"/>
       <c r="G777" s="1"/>
@@ -24279,7 +24279,7 @@
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="2"/>
-      <c r="D778" s="33"/>
+      <c r="D778" s="18"/>
       <c r="E778" s="3"/>
       <c r="F778" s="3"/>
       <c r="G778" s="1"/>
@@ -24308,7 +24308,7 @@
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="2"/>
-      <c r="D779" s="33"/>
+      <c r="D779" s="18"/>
       <c r="E779" s="3"/>
       <c r="F779" s="3"/>
       <c r="G779" s="1"/>
@@ -24337,7 +24337,7 @@
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="2"/>
-      <c r="D780" s="33"/>
+      <c r="D780" s="18"/>
       <c r="E780" s="3"/>
       <c r="F780" s="3"/>
       <c r="G780" s="1"/>
@@ -24366,7 +24366,7 @@
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="2"/>
-      <c r="D781" s="33"/>
+      <c r="D781" s="18"/>
       <c r="E781" s="3"/>
       <c r="F781" s="3"/>
       <c r="G781" s="1"/>
@@ -24395,7 +24395,7 @@
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="2"/>
-      <c r="D782" s="33"/>
+      <c r="D782" s="18"/>
       <c r="E782" s="3"/>
       <c r="F782" s="3"/>
       <c r="G782" s="1"/>
@@ -24424,7 +24424,7 @@
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="2"/>
-      <c r="D783" s="33"/>
+      <c r="D783" s="18"/>
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
       <c r="G783" s="1"/>
@@ -24453,7 +24453,7 @@
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="2"/>
-      <c r="D784" s="33"/>
+      <c r="D784" s="18"/>
       <c r="E784" s="3"/>
       <c r="F784" s="3"/>
       <c r="G784" s="1"/>
@@ -24482,7 +24482,7 @@
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="2"/>
-      <c r="D785" s="33"/>
+      <c r="D785" s="18"/>
       <c r="E785" s="3"/>
       <c r="F785" s="3"/>
       <c r="G785" s="1"/>
@@ -24511,7 +24511,7 @@
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="2"/>
-      <c r="D786" s="33"/>
+      <c r="D786" s="18"/>
       <c r="E786" s="3"/>
       <c r="F786" s="3"/>
       <c r="G786" s="1"/>
@@ -24540,7 +24540,7 @@
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="2"/>
-      <c r="D787" s="33"/>
+      <c r="D787" s="18"/>
       <c r="E787" s="3"/>
       <c r="F787" s="3"/>
       <c r="G787" s="1"/>
@@ -24569,7 +24569,7 @@
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="2"/>
-      <c r="D788" s="33"/>
+      <c r="D788" s="18"/>
       <c r="E788" s="3"/>
       <c r="F788" s="3"/>
       <c r="G788" s="1"/>
@@ -24598,7 +24598,7 @@
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="2"/>
-      <c r="D789" s="33"/>
+      <c r="D789" s="18"/>
       <c r="E789" s="3"/>
       <c r="F789" s="3"/>
       <c r="G789" s="1"/>
@@ -24627,7 +24627,7 @@
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="2"/>
-      <c r="D790" s="33"/>
+      <c r="D790" s="18"/>
       <c r="E790" s="3"/>
       <c r="F790" s="3"/>
       <c r="G790" s="1"/>
@@ -24656,7 +24656,7 @@
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="2"/>
-      <c r="D791" s="33"/>
+      <c r="D791" s="18"/>
       <c r="E791" s="3"/>
       <c r="F791" s="3"/>
       <c r="G791" s="1"/>
@@ -24685,7 +24685,7 @@
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="2"/>
-      <c r="D792" s="33"/>
+      <c r="D792" s="18"/>
       <c r="E792" s="3"/>
       <c r="F792" s="3"/>
       <c r="G792" s="1"/>
@@ -24714,7 +24714,7 @@
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="2"/>
-      <c r="D793" s="33"/>
+      <c r="D793" s="18"/>
       <c r="E793" s="3"/>
       <c r="F793" s="3"/>
       <c r="G793" s="1"/>
@@ -24743,7 +24743,7 @@
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="2"/>
-      <c r="D794" s="33"/>
+      <c r="D794" s="18"/>
       <c r="E794" s="3"/>
       <c r="F794" s="3"/>
       <c r="G794" s="1"/>
@@ -24772,7 +24772,7 @@
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="2"/>
-      <c r="D795" s="33"/>
+      <c r="D795" s="18"/>
       <c r="E795" s="3"/>
       <c r="F795" s="3"/>
       <c r="G795" s="1"/>
@@ -24801,7 +24801,7 @@
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="2"/>
-      <c r="D796" s="33"/>
+      <c r="D796" s="18"/>
       <c r="E796" s="3"/>
       <c r="F796" s="3"/>
       <c r="G796" s="1"/>
@@ -24830,7 +24830,7 @@
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="2"/>
-      <c r="D797" s="33"/>
+      <c r="D797" s="18"/>
       <c r="E797" s="3"/>
       <c r="F797" s="3"/>
       <c r="G797" s="1"/>
@@ -24859,7 +24859,7 @@
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="2"/>
-      <c r="D798" s="33"/>
+      <c r="D798" s="18"/>
       <c r="E798" s="3"/>
       <c r="F798" s="3"/>
       <c r="G798" s="1"/>
@@ -24888,7 +24888,7 @@
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="2"/>
-      <c r="D799" s="33"/>
+      <c r="D799" s="18"/>
       <c r="E799" s="3"/>
       <c r="F799" s="3"/>
       <c r="G799" s="1"/>
@@ -24917,7 +24917,7 @@
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="2"/>
-      <c r="D800" s="33"/>
+      <c r="D800" s="18"/>
       <c r="E800" s="3"/>
       <c r="F800" s="3"/>
       <c r="G800" s="1"/>
@@ -24946,7 +24946,7 @@
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="2"/>
-      <c r="D801" s="33"/>
+      <c r="D801" s="18"/>
       <c r="E801" s="3"/>
       <c r="F801" s="3"/>
       <c r="G801" s="1"/>
@@ -24975,7 +24975,7 @@
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="2"/>
-      <c r="D802" s="33"/>
+      <c r="D802" s="18"/>
       <c r="E802" s="3"/>
       <c r="F802" s="3"/>
       <c r="G802" s="1"/>
@@ -25004,7 +25004,7 @@
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="2"/>
-      <c r="D803" s="33"/>
+      <c r="D803" s="18"/>
       <c r="E803" s="3"/>
       <c r="F803" s="3"/>
       <c r="G803" s="1"/>
@@ -25033,7 +25033,7 @@
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="2"/>
-      <c r="D804" s="33"/>
+      <c r="D804" s="18"/>
       <c r="E804" s="3"/>
       <c r="F804" s="3"/>
       <c r="G804" s="1"/>
@@ -25062,7 +25062,7 @@
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="2"/>
-      <c r="D805" s="33"/>
+      <c r="D805" s="18"/>
       <c r="E805" s="3"/>
       <c r="F805" s="3"/>
       <c r="G805" s="1"/>
@@ -25091,7 +25091,7 @@
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="2"/>
-      <c r="D806" s="33"/>
+      <c r="D806" s="18"/>
       <c r="E806" s="3"/>
       <c r="F806" s="3"/>
       <c r="G806" s="1"/>
@@ -25120,7 +25120,7 @@
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="2"/>
-      <c r="D807" s="33"/>
+      <c r="D807" s="18"/>
       <c r="E807" s="3"/>
       <c r="F807" s="3"/>
       <c r="G807" s="1"/>
@@ -25149,7 +25149,7 @@
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="2"/>
-      <c r="D808" s="33"/>
+      <c r="D808" s="18"/>
       <c r="E808" s="3"/>
       <c r="F808" s="3"/>
       <c r="G808" s="1"/>
@@ -25178,7 +25178,7 @@
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="2"/>
-      <c r="D809" s="33"/>
+      <c r="D809" s="18"/>
       <c r="E809" s="3"/>
       <c r="F809" s="3"/>
       <c r="G809" s="1"/>
@@ -25207,7 +25207,7 @@
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="2"/>
-      <c r="D810" s="33"/>
+      <c r="D810" s="18"/>
       <c r="E810" s="3"/>
       <c r="F810" s="3"/>
       <c r="G810" s="1"/>
@@ -25236,7 +25236,7 @@
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="2"/>
-      <c r="D811" s="33"/>
+      <c r="D811" s="18"/>
       <c r="E811" s="3"/>
       <c r="F811" s="3"/>
       <c r="G811" s="1"/>
@@ -25265,7 +25265,7 @@
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="2"/>
-      <c r="D812" s="33"/>
+      <c r="D812" s="18"/>
       <c r="E812" s="3"/>
       <c r="F812" s="3"/>
       <c r="G812" s="1"/>
@@ -25294,7 +25294,7 @@
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="2"/>
-      <c r="D813" s="33"/>
+      <c r="D813" s="18"/>
       <c r="E813" s="3"/>
       <c r="F813" s="3"/>
       <c r="G813" s="1"/>
@@ -25323,7 +25323,7 @@
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="2"/>
-      <c r="D814" s="33"/>
+      <c r="D814" s="18"/>
       <c r="E814" s="3"/>
       <c r="F814" s="3"/>
       <c r="G814" s="1"/>
@@ -25352,7 +25352,7 @@
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="2"/>
-      <c r="D815" s="33"/>
+      <c r="D815" s="18"/>
       <c r="E815" s="3"/>
       <c r="F815" s="3"/>
       <c r="G815" s="1"/>
@@ -25381,7 +25381,7 @@
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="2"/>
-      <c r="D816" s="33"/>
+      <c r="D816" s="18"/>
       <c r="E816" s="3"/>
       <c r="F816" s="3"/>
       <c r="G816" s="1"/>
@@ -25410,7 +25410,7 @@
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="2"/>
-      <c r="D817" s="33"/>
+      <c r="D817" s="18"/>
       <c r="E817" s="3"/>
       <c r="F817" s="3"/>
       <c r="G817" s="1"/>
@@ -25439,7 +25439,7 @@
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="2"/>
-      <c r="D818" s="33"/>
+      <c r="D818" s="18"/>
       <c r="E818" s="3"/>
       <c r="F818" s="3"/>
       <c r="G818" s="1"/>
@@ -25468,7 +25468,7 @@
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="2"/>
-      <c r="D819" s="33"/>
+      <c r="D819" s="18"/>
       <c r="E819" s="3"/>
       <c r="F819" s="3"/>
       <c r="G819" s="1"/>
@@ -25497,7 +25497,7 @@
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="2"/>
-      <c r="D820" s="33"/>
+      <c r="D820" s="18"/>
       <c r="E820" s="3"/>
       <c r="F820" s="3"/>
       <c r="G820" s="1"/>
@@ -25526,7 +25526,7 @@
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="2"/>
-      <c r="D821" s="33"/>
+      <c r="D821" s="18"/>
       <c r="E821" s="3"/>
       <c r="F821" s="3"/>
       <c r="G821" s="1"/>
@@ -25555,7 +25555,7 @@
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="2"/>
-      <c r="D822" s="33"/>
+      <c r="D822" s="18"/>
       <c r="E822" s="3"/>
       <c r="F822" s="3"/>
       <c r="G822" s="1"/>
@@ -25584,7 +25584,7 @@
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="2"/>
-      <c r="D823" s="33"/>
+      <c r="D823" s="18"/>
       <c r="E823" s="3"/>
       <c r="F823" s="3"/>
       <c r="G823" s="1"/>
@@ -25613,7 +25613,7 @@
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="2"/>
-      <c r="D824" s="33"/>
+      <c r="D824" s="18"/>
       <c r="E824" s="3"/>
       <c r="F824" s="3"/>
       <c r="G824" s="1"/>
@@ -25642,7 +25642,7 @@
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="2"/>
-      <c r="D825" s="33"/>
+      <c r="D825" s="18"/>
       <c r="E825" s="3"/>
       <c r="F825" s="3"/>
       <c r="G825" s="1"/>
@@ -25671,7 +25671,7 @@
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="2"/>
-      <c r="D826" s="33"/>
+      <c r="D826" s="18"/>
       <c r="E826" s="3"/>
       <c r="F826" s="3"/>
       <c r="G826" s="1"/>
@@ -25700,7 +25700,7 @@
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="2"/>
-      <c r="D827" s="33"/>
+      <c r="D827" s="18"/>
       <c r="E827" s="3"/>
       <c r="F827" s="3"/>
       <c r="G827" s="1"/>
@@ -25729,7 +25729,7 @@
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="2"/>
-      <c r="D828" s="33"/>
+      <c r="D828" s="18"/>
       <c r="E828" s="3"/>
       <c r="F828" s="3"/>
       <c r="G828" s="1"/>
@@ -25758,7 +25758,7 @@
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="2"/>
-      <c r="D829" s="33"/>
+      <c r="D829" s="18"/>
       <c r="E829" s="3"/>
       <c r="F829" s="3"/>
       <c r="G829" s="1"/>
@@ -25787,7 +25787,7 @@
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="2"/>
-      <c r="D830" s="33"/>
+      <c r="D830" s="18"/>
       <c r="E830" s="3"/>
       <c r="F830" s="3"/>
       <c r="G830" s="1"/>
@@ -25816,7 +25816,7 @@
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="2"/>
-      <c r="D831" s="33"/>
+      <c r="D831" s="18"/>
       <c r="E831" s="3"/>
       <c r="F831" s="3"/>
       <c r="G831" s="1"/>
@@ -25845,7 +25845,7 @@
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="2"/>
-      <c r="D832" s="33"/>
+      <c r="D832" s="18"/>
       <c r="E832" s="3"/>
       <c r="F832" s="3"/>
       <c r="G832" s="1"/>
@@ -25874,7 +25874,7 @@
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="2"/>
-      <c r="D833" s="33"/>
+      <c r="D833" s="18"/>
       <c r="E833" s="3"/>
       <c r="F833" s="3"/>
       <c r="G833" s="1"/>
@@ -25903,7 +25903,7 @@
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="2"/>
-      <c r="D834" s="33"/>
+      <c r="D834" s="18"/>
       <c r="E834" s="3"/>
       <c r="F834" s="3"/>
       <c r="G834" s="1"/>
@@ -25932,7 +25932,7 @@
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="2"/>
-      <c r="D835" s="33"/>
+      <c r="D835" s="18"/>
       <c r="E835" s="3"/>
       <c r="F835" s="3"/>
       <c r="G835" s="1"/>
@@ -25961,7 +25961,7 @@
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="2"/>
-      <c r="D836" s="33"/>
+      <c r="D836" s="18"/>
       <c r="E836" s="3"/>
       <c r="F836" s="3"/>
       <c r="G836" s="1"/>
@@ -25990,7 +25990,7 @@
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="2"/>
-      <c r="D837" s="33"/>
+      <c r="D837" s="18"/>
       <c r="E837" s="3"/>
       <c r="F837" s="3"/>
       <c r="G837" s="1"/>
@@ -26019,7 +26019,7 @@
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="2"/>
-      <c r="D838" s="33"/>
+      <c r="D838" s="18"/>
       <c r="E838" s="3"/>
       <c r="F838" s="3"/>
       <c r="G838" s="1"/>
@@ -26048,7 +26048,7 @@
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="2"/>
-      <c r="D839" s="33"/>
+      <c r="D839" s="18"/>
       <c r="E839" s="3"/>
       <c r="F839" s="3"/>
       <c r="G839" s="1"/>
@@ -26077,7 +26077,7 @@
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="2"/>
-      <c r="D840" s="33"/>
+      <c r="D840" s="18"/>
       <c r="E840" s="3"/>
       <c r="F840" s="3"/>
       <c r="G840" s="1"/>
@@ -26106,7 +26106,7 @@
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="2"/>
-      <c r="D841" s="33"/>
+      <c r="D841" s="18"/>
       <c r="E841" s="3"/>
       <c r="F841" s="3"/>
       <c r="G841" s="1"/>
@@ -26135,7 +26135,7 @@
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="2"/>
-      <c r="D842" s="33"/>
+      <c r="D842" s="18"/>
       <c r="E842" s="3"/>
       <c r="F842" s="3"/>
       <c r="G842" s="1"/>
@@ -26164,7 +26164,7 @@
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="2"/>
-      <c r="D843" s="33"/>
+      <c r="D843" s="18"/>
       <c r="E843" s="3"/>
       <c r="F843" s="3"/>
       <c r="G843" s="1"/>
@@ -26193,7 +26193,7 @@
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="2"/>
-      <c r="D844" s="33"/>
+      <c r="D844" s="18"/>
       <c r="E844" s="3"/>
       <c r="F844" s="3"/>
       <c r="G844" s="1"/>
@@ -26222,7 +26222,7 @@
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="2"/>
-      <c r="D845" s="33"/>
+      <c r="D845" s="18"/>
       <c r="E845" s="3"/>
       <c r="F845" s="3"/>
       <c r="G845" s="1"/>
@@ -26251,7 +26251,7 @@
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="2"/>
-      <c r="D846" s="33"/>
+      <c r="D846" s="18"/>
       <c r="E846" s="3"/>
       <c r="F846" s="3"/>
       <c r="G846" s="1"/>
@@ -26280,7 +26280,7 @@
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="2"/>
-      <c r="D847" s="33"/>
+      <c r="D847" s="18"/>
       <c r="E847" s="3"/>
       <c r="F847" s="3"/>
       <c r="G847" s="1"/>
@@ -26309,7 +26309,7 @@
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="2"/>
-      <c r="D848" s="33"/>
+      <c r="D848" s="18"/>
       <c r="E848" s="3"/>
       <c r="F848" s="3"/>
       <c r="G848" s="1"/>
@@ -26338,7 +26338,7 @@
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="2"/>
-      <c r="D849" s="33"/>
+      <c r="D849" s="18"/>
       <c r="E849" s="3"/>
       <c r="F849" s="3"/>
       <c r="G849" s="1"/>
@@ -26367,7 +26367,7 @@
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="2"/>
-      <c r="D850" s="33"/>
+      <c r="D850" s="18"/>
       <c r="E850" s="3"/>
       <c r="F850" s="3"/>
       <c r="G850" s="1"/>
@@ -26396,7 +26396,7 @@
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="2"/>
-      <c r="D851" s="33"/>
+      <c r="D851" s="18"/>
       <c r="E851" s="3"/>
       <c r="F851" s="3"/>
       <c r="G851" s="1"/>
@@ -26425,7 +26425,7 @@
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="2"/>
-      <c r="D852" s="33"/>
+      <c r="D852" s="18"/>
       <c r="E852" s="3"/>
       <c r="F852" s="3"/>
       <c r="G852" s="1"/>
@@ -26454,7 +26454,7 @@
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="2"/>
-      <c r="D853" s="33"/>
+      <c r="D853" s="18"/>
       <c r="E853" s="3"/>
       <c r="F853" s="3"/>
       <c r="G853" s="1"/>
@@ -26483,7 +26483,7 @@
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="2"/>
-      <c r="D854" s="33"/>
+      <c r="D854" s="18"/>
       <c r="E854" s="3"/>
       <c r="F854" s="3"/>
       <c r="G854" s="1"/>
@@ -26512,7 +26512,7 @@
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="2"/>
-      <c r="D855" s="33"/>
+      <c r="D855" s="18"/>
       <c r="E855" s="3"/>
       <c r="F855" s="3"/>
       <c r="G855" s="1"/>
@@ -26541,7 +26541,7 @@
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="2"/>
-      <c r="D856" s="33"/>
+      <c r="D856" s="18"/>
       <c r="E856" s="3"/>
       <c r="F856" s="3"/>
       <c r="G856" s="1"/>
@@ -26570,7 +26570,7 @@
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="2"/>
-      <c r="D857" s="33"/>
+      <c r="D857" s="18"/>
       <c r="E857" s="3"/>
       <c r="F857" s="3"/>
       <c r="G857" s="1"/>
@@ -26599,7 +26599,7 @@
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="2"/>
-      <c r="D858" s="33"/>
+      <c r="D858" s="18"/>
       <c r="E858" s="3"/>
       <c r="F858" s="3"/>
       <c r="G858" s="1"/>
@@ -26628,7 +26628,7 @@
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="2"/>
-      <c r="D859" s="33"/>
+      <c r="D859" s="18"/>
       <c r="E859" s="3"/>
       <c r="F859" s="3"/>
       <c r="G859" s="1"/>
@@ -26657,7 +26657,7 @@
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="2"/>
-      <c r="D860" s="33"/>
+      <c r="D860" s="18"/>
       <c r="E860" s="3"/>
       <c r="F860" s="3"/>
       <c r="G860" s="1"/>
@@ -26686,7 +26686,7 @@
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="2"/>
-      <c r="D861" s="33"/>
+      <c r="D861" s="18"/>
       <c r="E861" s="3"/>
       <c r="F861" s="3"/>
       <c r="G861" s="1"/>
@@ -26715,7 +26715,7 @@
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="2"/>
-      <c r="D862" s="33"/>
+      <c r="D862" s="18"/>
       <c r="E862" s="3"/>
       <c r="F862" s="3"/>
       <c r="G862" s="1"/>
@@ -26744,7 +26744,7 @@
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="2"/>
-      <c r="D863" s="33"/>
+      <c r="D863" s="18"/>
       <c r="E863" s="3"/>
       <c r="F863" s="3"/>
       <c r="G863" s="1"/>
@@ -26773,7 +26773,7 @@
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="2"/>
-      <c r="D864" s="33"/>
+      <c r="D864" s="18"/>
       <c r="E864" s="3"/>
       <c r="F864" s="3"/>
       <c r="G864" s="1"/>
@@ -26802,7 +26802,7 @@
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="2"/>
-      <c r="D865" s="33"/>
+      <c r="D865" s="18"/>
       <c r="E865" s="3"/>
       <c r="F865" s="3"/>
       <c r="G865" s="1"/>
@@ -26831,7 +26831,7 @@
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="2"/>
-      <c r="D866" s="33"/>
+      <c r="D866" s="18"/>
       <c r="E866" s="3"/>
       <c r="F866" s="3"/>
       <c r="G866" s="1"/>
@@ -26860,7 +26860,7 @@
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="2"/>
-      <c r="D867" s="33"/>
+      <c r="D867" s="18"/>
       <c r="E867" s="3"/>
       <c r="F867" s="3"/>
       <c r="G867" s="1"/>
@@ -26889,7 +26889,7 @@
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="2"/>
-      <c r="D868" s="33"/>
+      <c r="D868" s="18"/>
       <c r="E868" s="3"/>
       <c r="F868" s="3"/>
       <c r="G868" s="1"/>
@@ -26918,7 +26918,7 @@
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="2"/>
-      <c r="D869" s="33"/>
+      <c r="D869" s="18"/>
       <c r="E869" s="3"/>
       <c r="F869" s="3"/>
       <c r="G869" s="1"/>
@@ -26947,7 +26947,7 @@
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="2"/>
-      <c r="D870" s="33"/>
+      <c r="D870" s="18"/>
       <c r="E870" s="3"/>
       <c r="F870" s="3"/>
       <c r="G870" s="1"/>
@@ -26976,7 +26976,7 @@
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="2"/>
-      <c r="D871" s="33"/>
+      <c r="D871" s="18"/>
       <c r="E871" s="3"/>
       <c r="F871" s="3"/>
       <c r="G871" s="1"/>
@@ -27005,7 +27005,7 @@
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="2"/>
-      <c r="D872" s="33"/>
+      <c r="D872" s="18"/>
       <c r="E872" s="3"/>
       <c r="F872" s="3"/>
       <c r="G872" s="1"/>
@@ -27034,7 +27034,7 @@
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="2"/>
-      <c r="D873" s="33"/>
+      <c r="D873" s="18"/>
       <c r="E873" s="3"/>
       <c r="F873" s="3"/>
       <c r="G873" s="1"/>
@@ -27063,7 +27063,7 @@
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="2"/>
-      <c r="D874" s="33"/>
+      <c r="D874" s="18"/>
       <c r="E874" s="3"/>
       <c r="F874" s="3"/>
       <c r="G874" s="1"/>
@@ -27092,7 +27092,7 @@
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="2"/>
-      <c r="D875" s="33"/>
+      <c r="D875" s="18"/>
       <c r="E875" s="3"/>
       <c r="F875" s="3"/>
       <c r="G875" s="1"/>
@@ -27121,7 +27121,7 @@
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="2"/>
-      <c r="D876" s="33"/>
+      <c r="D876" s="18"/>
       <c r="E876" s="3"/>
       <c r="F876" s="3"/>
       <c r="G876" s="1"/>
@@ -27150,7 +27150,7 @@
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="2"/>
-      <c r="D877" s="33"/>
+      <c r="D877" s="18"/>
       <c r="E877" s="3"/>
       <c r="F877" s="3"/>
       <c r="G877" s="1"/>
@@ -27179,7 +27179,7 @@
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="2"/>
-      <c r="D878" s="33"/>
+      <c r="D878" s="18"/>
       <c r="E878" s="3"/>
       <c r="F878" s="3"/>
       <c r="G878" s="1"/>
@@ -27208,7 +27208,7 @@
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="2"/>
-      <c r="D879" s="33"/>
+      <c r="D879" s="18"/>
       <c r="E879" s="3"/>
       <c r="F879" s="3"/>
       <c r="G879" s="1"/>
@@ -27237,7 +27237,7 @@
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="2"/>
-      <c r="D880" s="33"/>
+      <c r="D880" s="18"/>
       <c r="E880" s="3"/>
       <c r="F880" s="3"/>
       <c r="G880" s="1"/>
@@ -27266,7 +27266,7 @@
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="2"/>
-      <c r="D881" s="33"/>
+      <c r="D881" s="18"/>
       <c r="E881" s="3"/>
       <c r="F881" s="3"/>
       <c r="G881" s="1"/>
@@ -27295,7 +27295,7 @@
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="2"/>
-      <c r="D882" s="33"/>
+      <c r="D882" s="18"/>
       <c r="E882" s="3"/>
       <c r="F882" s="3"/>
       <c r="G882" s="1"/>
@@ -27324,7 +27324,7 @@
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="2"/>
-      <c r="D883" s="33"/>
+      <c r="D883" s="18"/>
       <c r="E883" s="3"/>
       <c r="F883" s="3"/>
       <c r="G883" s="1"/>
@@ -27353,7 +27353,7 @@
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="2"/>
-      <c r="D884" s="33"/>
+      <c r="D884" s="18"/>
       <c r="E884" s="3"/>
       <c r="F884" s="3"/>
       <c r="G884" s="1"/>
@@ -27382,7 +27382,7 @@
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="2"/>
-      <c r="D885" s="33"/>
+      <c r="D885" s="18"/>
       <c r="E885" s="3"/>
       <c r="F885" s="3"/>
       <c r="G885" s="1"/>
@@ -27411,7 +27411,7 @@
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="2"/>
-      <c r="D886" s="33"/>
+      <c r="D886" s="18"/>
       <c r="E886" s="3"/>
       <c r="F886" s="3"/>
       <c r="G886" s="1"/>
@@ -27440,7 +27440,7 @@
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="2"/>
-      <c r="D887" s="33"/>
+      <c r="D887" s="18"/>
       <c r="E887" s="3"/>
       <c r="F887" s="3"/>
       <c r="G887" s="1"/>
@@ -27469,7 +27469,7 @@
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="2"/>
-      <c r="D888" s="33"/>
+      <c r="D888" s="18"/>
       <c r="E888" s="3"/>
       <c r="F888" s="3"/>
       <c r="G888" s="1"/>
@@ -27498,7 +27498,7 @@
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="2"/>
-      <c r="D889" s="33"/>
+      <c r="D889" s="18"/>
       <c r="E889" s="3"/>
       <c r="F889" s="3"/>
       <c r="G889" s="1"/>
@@ -27527,7 +27527,7 @@
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="2"/>
-      <c r="D890" s="33"/>
+      <c r="D890" s="18"/>
       <c r="E890" s="3"/>
       <c r="F890" s="3"/>
       <c r="G890" s="1"/>
@@ -27556,7 +27556,7 @@
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="2"/>
-      <c r="D891" s="33"/>
+      <c r="D891" s="18"/>
       <c r="E891" s="3"/>
       <c r="F891" s="3"/>
       <c r="G891" s="1"/>
@@ -27585,7 +27585,7 @@
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="2"/>
-      <c r="D892" s="33"/>
+      <c r="D892" s="18"/>
       <c r="E892" s="3"/>
       <c r="F892" s="3"/>
       <c r="G892" s="1"/>
@@ -27614,7 +27614,7 @@
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="2"/>
-      <c r="D893" s="33"/>
+      <c r="D893" s="18"/>
       <c r="E893" s="3"/>
       <c r="F893" s="3"/>
       <c r="G893" s="1"/>
@@ -27643,7 +27643,7 @@
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="2"/>
-      <c r="D894" s="33"/>
+      <c r="D894" s="18"/>
       <c r="E894" s="3"/>
       <c r="F894" s="3"/>
       <c r="G894" s="1"/>
@@ -27672,7 +27672,7 @@
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="2"/>
-      <c r="D895" s="33"/>
+      <c r="D895" s="18"/>
       <c r="E895" s="3"/>
       <c r="F895" s="3"/>
       <c r="G895" s="1"/>
@@ -27701,7 +27701,7 @@
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="2"/>
-      <c r="D896" s="33"/>
+      <c r="D896" s="18"/>
       <c r="E896" s="3"/>
       <c r="F896" s="3"/>
       <c r="G896" s="1"/>
@@ -27730,7 +27730,7 @@
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="2"/>
-      <c r="D897" s="33"/>
+      <c r="D897" s="18"/>
       <c r="E897" s="3"/>
       <c r="F897" s="3"/>
       <c r="G897" s="1"/>
@@ -27759,7 +27759,7 @@
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="2"/>
-      <c r="D898" s="33"/>
+      <c r="D898" s="18"/>
       <c r="E898" s="3"/>
       <c r="F898" s="3"/>
       <c r="G898" s="1"/>
@@ -27788,7 +27788,7 @@
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="2"/>
-      <c r="D899" s="33"/>
+      <c r="D899" s="18"/>
       <c r="E899" s="3"/>
       <c r="F899" s="3"/>
       <c r="G899" s="1"/>
@@ -27817,7 +27817,7 @@
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="2"/>
-      <c r="D900" s="33"/>
+      <c r="D900" s="18"/>
       <c r="E900" s="3"/>
       <c r="F900" s="3"/>
       <c r="G900" s="1"/>
@@ -27846,7 +27846,7 @@
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="2"/>
-      <c r="D901" s="33"/>
+      <c r="D901" s="18"/>
       <c r="E901" s="3"/>
       <c r="F901" s="3"/>
       <c r="G901" s="1"/>
@@ -27875,7 +27875,7 @@
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="2"/>
-      <c r="D902" s="33"/>
+      <c r="D902" s="18"/>
       <c r="E902" s="3"/>
       <c r="F902" s="3"/>
       <c r="G902" s="1"/>
@@ -27904,7 +27904,7 @@
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="2"/>
-      <c r="D903" s="33"/>
+      <c r="D903" s="18"/>
       <c r="E903" s="3"/>
       <c r="F903" s="3"/>
       <c r="G903" s="1"/>
@@ -27933,7 +27933,7 @@
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="2"/>
-      <c r="D904" s="33"/>
+      <c r="D904" s="18"/>
       <c r="E904" s="3"/>
       <c r="F904" s="3"/>
       <c r="G904" s="1"/>
@@ -27962,7 +27962,7 @@
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="2"/>
-      <c r="D905" s="33"/>
+      <c r="D905" s="18"/>
       <c r="E905" s="3"/>
       <c r="F905" s="3"/>
       <c r="G905" s="1"/>
@@ -27991,7 +27991,7 @@
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="2"/>
-      <c r="D906" s="33"/>
+      <c r="D906" s="18"/>
       <c r="E906" s="3"/>
       <c r="F906" s="3"/>
       <c r="G906" s="1"/>
@@ -28020,7 +28020,7 @@
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="2"/>
-      <c r="D907" s="33"/>
+      <c r="D907" s="18"/>
       <c r="E907" s="3"/>
       <c r="F907" s="3"/>
       <c r="G907" s="1"/>
@@ -28049,7 +28049,7 @@
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="2"/>
-      <c r="D908" s="33"/>
+      <c r="D908" s="18"/>
       <c r="E908" s="3"/>
       <c r="F908" s="3"/>
       <c r="G908" s="1"/>
@@ -28078,7 +28078,7 @@
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="2"/>
-      <c r="D909" s="33"/>
+      <c r="D909" s="18"/>
       <c r="E909" s="3"/>
       <c r="F909" s="3"/>
       <c r="G909" s="1"/>
@@ -28107,7 +28107,7 @@
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="2"/>
-      <c r="D910" s="33"/>
+      <c r="D910" s="18"/>
       <c r="E910" s="3"/>
       <c r="F910" s="3"/>
       <c r="G910" s="1"/>
@@ -28136,7 +28136,7 @@
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="2"/>
-      <c r="D911" s="33"/>
+      <c r="D911" s="18"/>
       <c r="E911" s="3"/>
       <c r="F911" s="3"/>
       <c r="G911" s="1"/>
@@ -28165,7 +28165,7 @@
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="2"/>
-      <c r="D912" s="33"/>
+      <c r="D912" s="18"/>
       <c r="E912" s="3"/>
       <c r="F912" s="3"/>
       <c r="G912" s="1"/>
@@ -28194,7 +28194,7 @@
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="2"/>
-      <c r="D913" s="33"/>
+      <c r="D913" s="18"/>
       <c r="E913" s="3"/>
       <c r="F913" s="3"/>
       <c r="G913" s="1"/>
@@ -28223,7 +28223,7 @@
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="2"/>
-      <c r="D914" s="33"/>
+      <c r="D914" s="18"/>
       <c r="E914" s="3"/>
       <c r="F914" s="3"/>
       <c r="G914" s="1"/>
@@ -28252,7 +28252,7 @@
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="2"/>
-      <c r="D915" s="33"/>
+      <c r="D915" s="18"/>
       <c r="E915" s="3"/>
       <c r="F915" s="3"/>
       <c r="G915" s="1"/>
@@ -28281,7 +28281,7 @@
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="2"/>
-      <c r="D916" s="33"/>
+      <c r="D916" s="18"/>
       <c r="E916" s="3"/>
       <c r="F916" s="3"/>
       <c r="G916" s="1"/>
@@ -28310,7 +28310,7 @@
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="2"/>
-      <c r="D917" s="33"/>
+      <c r="D917" s="18"/>
       <c r="E917" s="3"/>
       <c r="F917" s="3"/>
       <c r="G917" s="1"/>
@@ -28339,7 +28339,7 @@
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="2"/>
-      <c r="D918" s="33"/>
+      <c r="D918" s="18"/>
       <c r="E918" s="3"/>
       <c r="F918" s="3"/>
       <c r="G918" s="1"/>
@@ -28368,7 +28368,7 @@
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="2"/>
-      <c r="D919" s="33"/>
+      <c r="D919" s="18"/>
       <c r="E919" s="3"/>
       <c r="F919" s="3"/>
       <c r="G919" s="1"/>
@@ -28397,7 +28397,7 @@
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="2"/>
-      <c r="D920" s="33"/>
+      <c r="D920" s="18"/>
       <c r="E920" s="3"/>
       <c r="F920" s="3"/>
       <c r="G920" s="1"/>
@@ -28426,7 +28426,7 @@
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="2"/>
-      <c r="D921" s="33"/>
+      <c r="D921" s="18"/>
       <c r="E921" s="3"/>
       <c r="F921" s="3"/>
       <c r="G921" s="1"/>
@@ -28455,7 +28455,7 @@
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="2"/>
-      <c r="D922" s="33"/>
+      <c r="D922" s="18"/>
       <c r="E922" s="3"/>
       <c r="F922" s="3"/>
       <c r="G922" s="1"/>
@@ -28484,7 +28484,7 @@
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="2"/>
-      <c r="D923" s="33"/>
+      <c r="D923" s="18"/>
       <c r="E923" s="3"/>
       <c r="F923" s="3"/>
       <c r="G923" s="1"/>
@@ -28513,7 +28513,7 @@
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="2"/>
-      <c r="D924" s="33"/>
+      <c r="D924" s="18"/>
       <c r="E924" s="3"/>
       <c r="F924" s="3"/>
       <c r="G924" s="1"/>
@@ -28542,7 +28542,7 @@
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="2"/>
-      <c r="D925" s="33"/>
+      <c r="D925" s="18"/>
       <c r="E925" s="3"/>
       <c r="F925" s="3"/>
       <c r="G925" s="1"/>
@@ -28571,7 +28571,7 @@
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="2"/>
-      <c r="D926" s="33"/>
+      <c r="D926" s="18"/>
       <c r="E926" s="3"/>
       <c r="F926" s="3"/>
       <c r="G926" s="1"/>
@@ -28600,7 +28600,7 @@
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="2"/>
-      <c r="D927" s="33"/>
+      <c r="D927" s="18"/>
       <c r="E927" s="3"/>
       <c r="F927" s="3"/>
       <c r="G927" s="1"/>
@@ -28629,7 +28629,7 @@
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="2"/>
-      <c r="D928" s="33"/>
+      <c r="D928" s="18"/>
       <c r="E928" s="3"/>
       <c r="F928" s="3"/>
       <c r="G928" s="1"/>
@@ -28658,7 +28658,7 @@
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="2"/>
-      <c r="D929" s="33"/>
+      <c r="D929" s="18"/>
       <c r="E929" s="3"/>
       <c r="F929" s="3"/>
       <c r="G929" s="1"/>
@@ -28687,7 +28687,7 @@
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="2"/>
-      <c r="D930" s="33"/>
+      <c r="D930" s="18"/>
       <c r="E930" s="3"/>
       <c r="F930" s="3"/>
       <c r="G930" s="1"/>
@@ -28716,7 +28716,7 @@
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="2"/>
-      <c r="D931" s="33"/>
+      <c r="D931" s="18"/>
       <c r="E931" s="3"/>
       <c r="F931" s="3"/>
       <c r="G931" s="1"/>
@@ -28745,7 +28745,7 @@
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="2"/>
-      <c r="D932" s="33"/>
+      <c r="D932" s="18"/>
       <c r="E932" s="3"/>
       <c r="F932" s="3"/>
       <c r="G932" s="1"/>
@@ -28774,7 +28774,7 @@
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="2"/>
-      <c r="D933" s="33"/>
+      <c r="D933" s="18"/>
       <c r="E933" s="3"/>
       <c r="F933" s="3"/>
       <c r="G933" s="1"/>
@@ -28803,7 +28803,7 @@
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="2"/>
-      <c r="D934" s="33"/>
+      <c r="D934" s="18"/>
       <c r="E934" s="3"/>
       <c r="F934" s="3"/>
       <c r="G934" s="1"/>
@@ -28832,7 +28832,7 @@
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="2"/>
-      <c r="D935" s="33"/>
+      <c r="D935" s="18"/>
       <c r="E935" s="3"/>
       <c r="F935" s="3"/>
       <c r="G935" s="1"/>
@@ -28861,7 +28861,7 @@
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="2"/>
-      <c r="D936" s="33"/>
+      <c r="D936" s="18"/>
       <c r="E936" s="3"/>
       <c r="F936" s="3"/>
       <c r="G936" s="1"/>
@@ -28890,7 +28890,7 @@
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="2"/>
-      <c r="D937" s="33"/>
+      <c r="D937" s="18"/>
       <c r="E937" s="3"/>
       <c r="F937" s="3"/>
       <c r="G937" s="1"/>
@@ -28919,7 +28919,7 @@
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="2"/>
-      <c r="D938" s="33"/>
+      <c r="D938" s="18"/>
       <c r="E938" s="3"/>
       <c r="F938" s="3"/>
       <c r="G938" s="1"/>
@@ -28948,7 +28948,7 @@
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="2"/>
-      <c r="D939" s="33"/>
+      <c r="D939" s="18"/>
       <c r="E939" s="3"/>
       <c r="F939" s="3"/>
       <c r="G939" s="1"/>
@@ -28977,7 +28977,7 @@
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="2"/>
-      <c r="D940" s="33"/>
+      <c r="D940" s="18"/>
       <c r="E940" s="3"/>
       <c r="F940" s="3"/>
       <c r="G940" s="1"/>
@@ -29006,7 +29006,7 @@
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="2"/>
-      <c r="D941" s="33"/>
+      <c r="D941" s="18"/>
       <c r="E941" s="3"/>
       <c r="F941" s="3"/>
       <c r="G941" s="1"/>
@@ -29035,7 +29035,7 @@
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="2"/>
-      <c r="D942" s="33"/>
+      <c r="D942" s="18"/>
       <c r="E942" s="3"/>
       <c r="F942" s="3"/>
       <c r="G942" s="1"/>
@@ -29064,7 +29064,7 @@
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="2"/>
-      <c r="D943" s="33"/>
+      <c r="D943" s="18"/>
       <c r="E943" s="3"/>
       <c r="F943" s="3"/>
       <c r="G943" s="1"/>
@@ -29093,7 +29093,7 @@
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="2"/>
-      <c r="D944" s="33"/>
+      <c r="D944" s="18"/>
       <c r="E944" s="3"/>
       <c r="F944" s="3"/>
       <c r="G944" s="1"/>
@@ -29122,7 +29122,7 @@
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="2"/>
-      <c r="D945" s="33"/>
+      <c r="D945" s="18"/>
       <c r="E945" s="3"/>
       <c r="F945" s="3"/>
       <c r="G945" s="1"/>
@@ -29151,7 +29151,7 @@
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="2"/>
-      <c r="D946" s="33"/>
+      <c r="D946" s="18"/>
       <c r="E946" s="3"/>
       <c r="F946" s="3"/>
       <c r="G946" s="1"/>
@@ -29180,7 +29180,7 @@
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="2"/>
-      <c r="D947" s="33"/>
+      <c r="D947" s="18"/>
       <c r="E947" s="3"/>
       <c r="F947" s="3"/>
       <c r="G947" s="1"/>
@@ -29209,7 +29209,7 @@
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="2"/>
-      <c r="D948" s="33"/>
+      <c r="D948" s="18"/>
       <c r="E948" s="3"/>
       <c r="F948" s="3"/>
       <c r="G948" s="1"/>
@@ -29238,7 +29238,7 @@
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="2"/>
-      <c r="D949" s="33"/>
+      <c r="D949" s="18"/>
       <c r="E949" s="3"/>
       <c r="F949" s="3"/>
       <c r="G949" s="1"/>
@@ -29267,7 +29267,7 @@
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="2"/>
-      <c r="D950" s="33"/>
+      <c r="D950" s="18"/>
       <c r="E950" s="3"/>
       <c r="F950" s="3"/>
       <c r="G950" s="1"/>
@@ -29296,7 +29296,7 @@
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="2"/>
-      <c r="D951" s="33"/>
+      <c r="D951" s="18"/>
       <c r="E951" s="3"/>
       <c r="F951" s="3"/>
       <c r="G951" s="1"/>
@@ -29325,7 +29325,7 @@
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="2"/>
-      <c r="D952" s="33"/>
+      <c r="D952" s="18"/>
       <c r="E952" s="3"/>
       <c r="F952" s="3"/>
       <c r="G952" s="1"/>
@@ -29354,7 +29354,7 @@
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="2"/>
-      <c r="D953" s="33"/>
+      <c r="D953" s="18"/>
       <c r="E953" s="3"/>
       <c r="F953" s="3"/>
       <c r="G953" s="1"/>
@@ -29383,7 +29383,7 @@
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="2"/>
-      <c r="D954" s="33"/>
+      <c r="D954" s="18"/>
       <c r="E954" s="3"/>
       <c r="F954" s="3"/>
       <c r="G954" s="1"/>
@@ -29412,7 +29412,7 @@
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="2"/>
-      <c r="D955" s="33"/>
+      <c r="D955" s="18"/>
       <c r="E955" s="3"/>
       <c r="F955" s="3"/>
       <c r="G955" s="1"/>
@@ -29441,7 +29441,7 @@
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="2"/>
-      <c r="D956" s="33"/>
+      <c r="D956" s="18"/>
       <c r="E956" s="3"/>
       <c r="F956" s="3"/>
       <c r="G956" s="1"/>
@@ -29470,7 +29470,7 @@
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="2"/>
-      <c r="D957" s="33"/>
+      <c r="D957" s="18"/>
       <c r="E957" s="3"/>
       <c r="F957" s="3"/>
       <c r="G957" s="1"/>
@@ -29499,7 +29499,7 @@
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="2"/>
-      <c r="D958" s="33"/>
+      <c r="D958" s="18"/>
       <c r="E958" s="3"/>
       <c r="F958" s="3"/>
       <c r="G958" s="1"/>
@@ -29528,7 +29528,7 @@
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="2"/>
-      <c r="D959" s="33"/>
+      <c r="D959" s="18"/>
       <c r="E959" s="3"/>
       <c r="F959" s="3"/>
       <c r="G959" s="1"/>
@@ -29557,7 +29557,7 @@
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="2"/>
-      <c r="D960" s="33"/>
+      <c r="D960" s="18"/>
       <c r="E960" s="3"/>
       <c r="F960" s="3"/>
       <c r="G960" s="1"/>
@@ -29586,7 +29586,7 @@
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="2"/>
-      <c r="D961" s="33"/>
+      <c r="D961" s="18"/>
       <c r="E961" s="3"/>
       <c r="F961" s="3"/>
       <c r="G961" s="1"/>
@@ -29615,7 +29615,7 @@
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="2"/>
-      <c r="D962" s="33"/>
+      <c r="D962" s="18"/>
       <c r="E962" s="3"/>
       <c r="F962" s="3"/>
       <c r="G962" s="1"/>
@@ -29644,7 +29644,7 @@
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="2"/>
-      <c r="D963" s="33"/>
+      <c r="D963" s="18"/>
       <c r="E963" s="3"/>
       <c r="F963" s="3"/>
       <c r="G963" s="1"/>
@@ -29673,7 +29673,7 @@
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="2"/>
-      <c r="D964" s="33"/>
+      <c r="D964" s="18"/>
       <c r="E964" s="3"/>
       <c r="F964" s="3"/>
       <c r="G964" s="1"/>
@@ -29702,7 +29702,7 @@
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="2"/>
-      <c r="D965" s="33"/>
+      <c r="D965" s="18"/>
       <c r="E965" s="3"/>
       <c r="F965" s="3"/>
       <c r="G965" s="1"/>
@@ -29731,7 +29731,7 @@
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="2"/>
-      <c r="D966" s="33"/>
+      <c r="D966" s="18"/>
       <c r="E966" s="3"/>
       <c r="F966" s="3"/>
       <c r="G966" s="1"/>
@@ -29760,7 +29760,7 @@
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="2"/>
-      <c r="D967" s="33"/>
+      <c r="D967" s="18"/>
       <c r="E967" s="3"/>
       <c r="F967" s="3"/>
       <c r="G967" s="1"/>
@@ -29789,7 +29789,7 @@
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="2"/>
-      <c r="D968" s="33"/>
+      <c r="D968" s="18"/>
       <c r="E968" s="3"/>
       <c r="F968" s="3"/>
       <c r="G968" s="1"/>
@@ -29818,7 +29818,7 @@
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="2"/>
-      <c r="D969" s="33"/>
+      <c r="D969" s="18"/>
       <c r="E969" s="3"/>
       <c r="F969" s="3"/>
       <c r="G969" s="1"/>
@@ -29847,7 +29847,7 @@
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="2"/>
-      <c r="D970" s="33"/>
+      <c r="D970" s="18"/>
       <c r="E970" s="3"/>
       <c r="F970" s="3"/>
       <c r="G970" s="1"/>
@@ -29876,7 +29876,7 @@
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="2"/>
-      <c r="D971" s="33"/>
+      <c r="D971" s="18"/>
       <c r="E971" s="3"/>
       <c r="F971" s="3"/>
       <c r="G971" s="1"/>
@@ -29905,7 +29905,7 @@
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="2"/>
-      <c r="D972" s="33"/>
+      <c r="D972" s="18"/>
       <c r="E972" s="3"/>
       <c r="F972" s="3"/>
       <c r="G972" s="1"/>
@@ -29934,7 +29934,7 @@
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="2"/>
-      <c r="D973" s="33"/>
+      <c r="D973" s="18"/>
       <c r="E973" s="3"/>
       <c r="F973" s="3"/>
       <c r="G973" s="1"/>
@@ -29963,7 +29963,7 @@
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="2"/>
-      <c r="D974" s="33"/>
+      <c r="D974" s="18"/>
       <c r="E974" s="3"/>
       <c r="F974" s="3"/>
       <c r="G974" s="1"/>
@@ -29992,7 +29992,7 @@
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="2"/>
-      <c r="D975" s="33"/>
+      <c r="D975" s="18"/>
       <c r="E975" s="3"/>
       <c r="F975" s="3"/>
       <c r="G975" s="1"/>
@@ -30021,7 +30021,7 @@
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="2"/>
-      <c r="D976" s="33"/>
+      <c r="D976" s="18"/>
       <c r="E976" s="3"/>
       <c r="F976" s="3"/>
       <c r="G976" s="1"/>
@@ -30050,7 +30050,7 @@
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="2"/>
-      <c r="D977" s="33"/>
+      <c r="D977" s="18"/>
       <c r="E977" s="3"/>
       <c r="F977" s="3"/>
       <c r="G977" s="1"/>
@@ -30079,7 +30079,7 @@
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="2"/>
-      <c r="D978" s="33"/>
+      <c r="D978" s="18"/>
       <c r="E978" s="3"/>
       <c r="F978" s="3"/>
       <c r="G978" s="1"/>
@@ -30108,7 +30108,7 @@
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="2"/>
-      <c r="D979" s="33"/>
+      <c r="D979" s="18"/>
       <c r="E979" s="3"/>
       <c r="F979" s="3"/>
       <c r="G979" s="1"/>
@@ -30137,7 +30137,7 @@
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="2"/>
-      <c r="D980" s="33"/>
+      <c r="D980" s="18"/>
       <c r="E980" s="3"/>
       <c r="F980" s="3"/>
       <c r="G980" s="1"/>
@@ -30166,7 +30166,7 @@
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="2"/>
-      <c r="D981" s="33"/>
+      <c r="D981" s="18"/>
       <c r="E981" s="3"/>
       <c r="F981" s="3"/>
       <c r="G981" s="1"/>
@@ -30195,7 +30195,7 @@
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="2"/>
-      <c r="D982" s="33"/>
+      <c r="D982" s="18"/>
       <c r="E982" s="3"/>
       <c r="F982" s="3"/>
       <c r="G982" s="1"/>
@@ -30224,7 +30224,7 @@
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="2"/>
-      <c r="D983" s="33"/>
+      <c r="D983" s="18"/>
       <c r="E983" s="3"/>
       <c r="F983" s="3"/>
       <c r="G983" s="1"/>
@@ -30253,7 +30253,7 @@
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="2"/>
-      <c r="D984" s="33"/>
+      <c r="D984" s="18"/>
       <c r="E984" s="3"/>
       <c r="F984" s="3"/>
       <c r="G984" s="1"/>
@@ -30282,7 +30282,7 @@
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="2"/>
-      <c r="D985" s="33"/>
+      <c r="D985" s="18"/>
       <c r="E985" s="3"/>
       <c r="F985" s="3"/>
       <c r="G985" s="1"/>
@@ -30311,7 +30311,7 @@
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="2"/>
-      <c r="D986" s="33"/>
+      <c r="D986" s="18"/>
       <c r="E986" s="3"/>
       <c r="F986" s="3"/>
       <c r="G986" s="1"/>
@@ -30340,7 +30340,7 @@
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="2"/>
-      <c r="D987" s="33"/>
+      <c r="D987" s="18"/>
       <c r="E987" s="3"/>
       <c r="F987" s="3"/>
       <c r="G987" s="1"/>
@@ -30369,7 +30369,7 @@
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="2"/>
-      <c r="D988" s="33"/>
+      <c r="D988" s="18"/>
       <c r="E988" s="3"/>
       <c r="F988" s="3"/>
       <c r="G988" s="1"/>
@@ -30398,7 +30398,7 @@
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="2"/>
-      <c r="D989" s="33"/>
+      <c r="D989" s="18"/>
       <c r="E989" s="3"/>
       <c r="F989" s="3"/>
       <c r="G989" s="1"/>
@@ -30427,7 +30427,7 @@
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="2"/>
-      <c r="D990" s="33"/>
+      <c r="D990" s="18"/>
       <c r="E990" s="3"/>
       <c r="F990" s="3"/>
       <c r="G990" s="1"/>
@@ -30456,7 +30456,7 @@
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="2"/>
-      <c r="D991" s="33"/>
+      <c r="D991" s="18"/>
       <c r="E991" s="3"/>
       <c r="F991" s="3"/>
       <c r="G991" s="1"/>
@@ -30485,7 +30485,7 @@
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="2"/>
-      <c r="D992" s="33"/>
+      <c r="D992" s="18"/>
       <c r="E992" s="3"/>
       <c r="F992" s="3"/>
       <c r="G992" s="1"/>
@@ -30514,7 +30514,7 @@
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="2"/>
-      <c r="D993" s="33"/>
+      <c r="D993" s="18"/>
       <c r="E993" s="3"/>
       <c r="F993" s="3"/>
       <c r="G993" s="1"/>
@@ -30543,7 +30543,7 @@
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="2"/>
-      <c r="D994" s="33"/>
+      <c r="D994" s="18"/>
       <c r="E994" s="3"/>
       <c r="F994" s="3"/>
       <c r="G994" s="1"/>
@@ -30572,7 +30572,7 @@
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="2"/>
-      <c r="D995" s="33"/>
+      <c r="D995" s="18"/>
       <c r="E995" s="3"/>
       <c r="F995" s="3"/>
       <c r="G995" s="1"/>
@@ -30601,7 +30601,7 @@
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="2"/>
-      <c r="D996" s="33"/>
+      <c r="D996" s="18"/>
       <c r="E996" s="3"/>
       <c r="F996" s="3"/>
       <c r="G996" s="1"/>
@@ -30630,7 +30630,7 @@
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="2"/>
-      <c r="D997" s="33"/>
+      <c r="D997" s="18"/>
       <c r="E997" s="3"/>
       <c r="F997" s="3"/>
       <c r="G997" s="1"/>
@@ -30659,7 +30659,7 @@
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="2"/>
-      <c r="D998" s="33"/>
+      <c r="D998" s="18"/>
       <c r="E998" s="3"/>
       <c r="F998" s="3"/>
       <c r="G998" s="1"/>
@@ -30688,7 +30688,7 @@
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="2"/>
-      <c r="D999" s="33"/>
+      <c r="D999" s="18"/>
       <c r="E999" s="3"/>
       <c r="F999" s="3"/>
       <c r="G999" s="1"/>
@@ -30717,7 +30717,7 @@
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="2"/>
-      <c r="D1000" s="33"/>
+      <c r="D1000" s="18"/>
       <c r="E1000" s="3"/>
       <c r="F1000" s="3"/>
       <c r="G1000" s="1"/>
@@ -30746,7 +30746,7 @@
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="2"/>
-      <c r="D1001" s="33"/>
+      <c r="D1001" s="18"/>
       <c r="E1001" s="3"/>
       <c r="F1001" s="3"/>
       <c r="G1001" s="1"/>
@@ -30773,6 +30773,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="B30:B35"/>
@@ -30787,19 +30800,6 @@
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
